--- a/MSW_pathway_model_v3/outputs/user_reports/my_cities_report.xlsx
+++ b/MSW_pathway_model_v3/outputs/user_reports/my_cities_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Selisih peluang di bawah 0,05 dianggap seri secara statistik.</t>
+          <t>Opsi terbaik adalah yang biaya dengan valuasi karbonnya, C + pG/1000 (USD/t), paling rendah untuk nilai karbon p yang dipilih. Ini bukan biaya sosial penuh: dampak kesehatan dan polusi lokal tidak dinilai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Selisih peluang yang kecil berarti pilihan bergantung pada input yang masih tidak pasti (ketidakpastian keputusan), bukan derau Monte Carlo; galat baku dilaporkan dan nilainya kecil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fasilitas belum ada: hasil ini penapisan ex-ante untuk menentukan opsi yang layak dikaji, dilelang, atau dipilotkan, dan data mana yang perlu dikumpulkan lebih dulu.</t>
         </is>
       </c>
     </row>
@@ -578,19 +592,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E3" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="F3" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G3" t="n">
         <v>49.1</v>
       </c>
       <c r="H3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" t="n">
         <v>-5579</v>
@@ -623,10 +637,10 @@
         <v>317</v>
       </c>
       <c r="G4" t="n">
-        <v>27.1</v>
+        <v>36.5</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="I4" t="n">
         <v>-5768</v>
@@ -650,22 +664,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="E5" t="n">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F5" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>29.9</v>
+        <v>34.8</v>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="I5" t="n">
-        <v>-258</v>
+        <v>-40</v>
       </c>
       <c r="J5" t="n">
         <v>0.07199999999999999</v>
@@ -722,22 +736,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="F7" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G7" t="n">
-        <v>29.3</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="I7" t="n">
-        <v>-6288</v>
+        <v>-6070</v>
       </c>
       <c r="J7" t="n">
         <v>0.042</v>
@@ -792,19 +806,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E9" t="n">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F9" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G9" t="n">
         <v>120.3</v>
       </c>
       <c r="H9" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I9" t="n">
         <v>-4772</v>
@@ -831,16 +845,16 @@
         <v>272</v>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F10" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G10" t="n">
-        <v>61.3</v>
+        <v>70.2</v>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I10" t="n">
         <v>-4604</v>
@@ -864,22 +878,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="E11" t="n">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="F11" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>60.6</v>
+        <v>65.8</v>
       </c>
       <c r="H11" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="I11" t="n">
-        <v>-325</v>
+        <v>-80</v>
       </c>
       <c r="J11" t="n">
         <v>0.07000000000000001</v>
@@ -936,22 +950,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E13" t="n">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="F13" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G13" t="n">
-        <v>66.7</v>
+        <v>78.2</v>
       </c>
       <c r="H13" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I13" t="n">
-        <v>-5188</v>
+        <v>-4944</v>
       </c>
       <c r="J13" t="n">
         <v>0.043</v>
@@ -968,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,47 +998,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>carbon_value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>most_probable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>p_most_probable</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mc_se</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>lead</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>tie</t>
         </is>
       </c>
     </row>
@@ -1036,37 +1060,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Makanan terpilah</t>
+          <t>Pasar</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004</v>
+        <v>0.965</v>
       </c>
       <c r="E2" t="n">
-        <v>0.103</v>
+        <v>0.003</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3310000000000001</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
+        <v>0.032</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.005811626278418119</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9329999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1081,33 +1111,39 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.287</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004</v>
+        <v>0.965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.105</v>
+        <v>0.003</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>0.032</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.005811626278418119</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9329999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1118,37 +1154,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kadar air IPCC</t>
+          <t>Pasar</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.119</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.041</v>
+        <v>0.929</v>
       </c>
       <c r="E4" t="n">
-        <v>0.047</v>
+        <v>0.017</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G4" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.657</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.008121514637061239</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.894</v>
       </c>
     </row>
     <row r="5">
@@ -1159,78 +1201,90 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tarif Perpres 109/2025</t>
+          <t>Pasar</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.287</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.105</v>
+        <v>0.039</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
+        <v>0.028</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01570830990272346</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3270000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kota Magelang</t>
+          <t>Kab. Pati</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Makanan terpilah</t>
+          <t>Pasar</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.466</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.068</v>
+        <v>0.026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.206</v>
+        <v>0.047</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
+        <v>0.008</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01159310139695155</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.761</v>
       </c>
     </row>
     <row r="7">
@@ -1245,13 +1299,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1260,18 +1314,24 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1282,37 +1342,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kadar air IPCC</t>
+          <t>Pasar</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.398</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1323,37 +1389,1547 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Pasar</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.00141279864099595</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pasar</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009612023720320294</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.843</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pasar</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01574722197722506</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.213</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Tarif Perpres 109/2025</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
+      <c r="K12" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.005811626278418119</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9329999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.005811626278418119</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.9329999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.008121514637061239</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.894</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.01570830990272346</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3270000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01159310139695155</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.761</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.00141279864099595</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.009612023720320294</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.843</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tarif Perpres 109/2025</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.01574722197722506</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.213</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.006956938982052382</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.9169999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.007451107300260817</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9089999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.01577035193012508</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.01580224667571039</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.232</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.01220147532063234</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6559999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.002817090697865442</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.002986469487538757</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.01138380428503582</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.696</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>50</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.01579607546196206</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.02699999999999997</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Makanan terpilah</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0158088266484265</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.00997276290703835</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.829</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.01020176455325254</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8180000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.01548544477888834</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.392</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.01554142850577128</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.361</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kab. Pati</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>100</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.01116619899518184</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.003298332912245217</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>50</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.01503246486774541</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.378</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kadar air IPCC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>100</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.009612023720320294</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.8300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +3009,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1503,7 +3079,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1573,7 +3149,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1613,7 +3189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
     </row>
@@ -1638,7 +3214,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1678,7 +3254,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1909,7 +3485,7 @@
         <v>17.793</v>
       </c>
       <c r="O2" t="n">
-        <v>44.863</v>
+        <v>26.918</v>
       </c>
       <c r="P2" t="n">
         <v>8.013999999999999</v>
@@ -2013,7 +3589,7 @@
         <v>17.422</v>
       </c>
       <c r="O3" t="n">
-        <v>50.396</v>
+        <v>30.238</v>
       </c>
       <c r="P3" t="n">
         <v>10.374</v>
@@ -2082,7 +3658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AQ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,120 +3709,170 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>p_best_at_0</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>p_best_at_0_se</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>p_best_at_2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>p_best_at_2_se</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>p_best_at_25</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>p_best_at_25_se</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>p_best_at_50</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>p_best_at_50_se</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>p_best_at_100</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>p_best_at_100_se</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>G_p5</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>G_p50</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>G_p95</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>C_p5</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>C_p50</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>C_p95</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>dG_OD_p5</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dG_OD_p50</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dG_OD_p95</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dC_OD_p5</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dC_OD_p50</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dC_OD_p95</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dG_SL_p5</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dG_SL_p50</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dG_SL_p95</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dC_SL_p5</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dC_SL_p50</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dC_SL_p95</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>CED_p5</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>CED_p50</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>CED_p95</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>LU_p5</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>LU_p50</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>LU_p95</t>
         </is>
@@ -2272,91 +3898,121 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.287</v>
+        <v>0.53</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9216</v>
+        <v>0.9804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4334</v>
+        <v>0.7833</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0524</v>
+        <v>0.2524</v>
       </c>
       <c r="J2" t="n">
-        <v>246.3381</v>
+        <v>0.965</v>
       </c>
       <c r="K2" t="n">
-        <v>443.768</v>
+        <v>0.0058</v>
       </c>
       <c r="L2" t="n">
-        <v>713.5906</v>
+        <v>0.965</v>
       </c>
       <c r="M2" t="n">
-        <v>13.1844</v>
+        <v>0.0058</v>
       </c>
       <c r="N2" t="n">
-        <v>18.5342</v>
+        <v>0.929</v>
       </c>
       <c r="O2" t="n">
-        <v>24.0167</v>
+        <v>0.0081</v>
       </c>
       <c r="P2" t="n">
-        <v>7.8567</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>234.4638</v>
+        <v>0.0157</v>
       </c>
       <c r="R2" t="n">
-        <v>478.4843</v>
+        <v>0.079</v>
       </c>
       <c r="S2" t="n">
-        <v>8.506600000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>14.0447</v>
+        <v>260.2313</v>
       </c>
       <c r="U2" t="n">
-        <v>19.4774</v>
+        <v>473.4537</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>789.3863</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>11.0104</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>17.8314</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>23.7686</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-47.8277</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>200.9614</v>
       </c>
       <c r="AB2" t="n">
-        <v>49.2936</v>
+        <v>483.4878</v>
       </c>
       <c r="AC2" t="n">
-        <v>87.13500000000001</v>
+        <v>6.4758</v>
       </c>
       <c r="AD2" t="n">
-        <v>137.2735</v>
+        <v>13.3336</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0577</v>
+        <v>19.1865</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1311</v>
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>50.297</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>87.25320000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>138.0239</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="3">
@@ -2376,94 +4032,124 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.95</v>
+        <v>0.948</v>
       </c>
       <c r="E3" t="n">
-        <v>0.044</v>
+        <v>0.148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004</v>
+        <v>0.034</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0078</v>
+        <v>0.0261</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0019</v>
+        <v>0.0466</v>
       </c>
       <c r="J3" t="n">
-        <v>33.792</v>
+        <v>0.003</v>
       </c>
       <c r="K3" t="n">
-        <v>201.4027</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" t="n">
-        <v>398.9821</v>
+        <v>0.003</v>
       </c>
       <c r="M3" t="n">
-        <v>32.9201</v>
+        <v>0.0017</v>
       </c>
       <c r="N3" t="n">
-        <v>54.6282</v>
+        <v>0.017</v>
       </c>
       <c r="O3" t="n">
-        <v>76.25149999999999</v>
+        <v>0.0041</v>
       </c>
       <c r="P3" t="n">
-        <v>121.5295</v>
+        <v>0.039</v>
       </c>
       <c r="Q3" t="n">
-        <v>481.8229</v>
+        <v>0.0061</v>
       </c>
       <c r="R3" t="n">
-        <v>880.0793</v>
+        <v>0.026</v>
       </c>
       <c r="S3" t="n">
-        <v>28.8776</v>
+        <v>0.005</v>
       </c>
       <c r="T3" t="n">
-        <v>49.7468</v>
+        <v>32.0236</v>
       </c>
       <c r="U3" t="n">
-        <v>71.6972</v>
+        <v>198.8733</v>
       </c>
       <c r="V3" t="n">
-        <v>-85.7073</v>
+        <v>407.6857</v>
       </c>
       <c r="W3" t="n">
-        <v>242.1789</v>
+        <v>33.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>591.9087</v>
+        <v>53.6771</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.3887</v>
+        <v>75.95829999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>35.6789</v>
+        <v>101.4053</v>
       </c>
       <c r="AA3" t="n">
-        <v>59.524</v>
+        <v>493.8181</v>
       </c>
       <c r="AB3" t="n">
-        <v>-7576.136</v>
+        <v>899.9864</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5178.3622</v>
+        <v>27.936</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3475.005</v>
+        <v>49.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0137</v>
+        <v>71.1116</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0189</v>
+        <v>-75.4547</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0275</v>
+        <v>272.5886</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>677.4353</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>14.6323</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>36.1389</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>58.2405</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-7767.744</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-5200.1019</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-3467.9598</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.0267</v>
       </c>
     </row>
     <row r="4">
@@ -2486,91 +4172,121 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="F4" t="n">
-        <v>0.105</v>
+        <v>0.075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1932</v>
+        <v>0.0731</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0485</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.0382</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>129.9706</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>267.7732</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>19.8853</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>28.5365</v>
+        <v>0.016</v>
       </c>
       <c r="O4" t="n">
-        <v>36.7816</v>
+        <v>0.004</v>
       </c>
       <c r="P4" t="n">
-        <v>306.4469</v>
+        <v>0.146</v>
       </c>
       <c r="Q4" t="n">
-        <v>552.4836</v>
+        <v>0.0112</v>
       </c>
       <c r="R4" t="n">
-        <v>886.1239</v>
+        <v>0.047</v>
       </c>
       <c r="S4" t="n">
-        <v>15.1516</v>
+        <v>0.0067</v>
       </c>
       <c r="T4" t="n">
-        <v>23.708</v>
+        <v>0.9105</v>
       </c>
       <c r="U4" t="n">
-        <v>32.3943</v>
+        <v>142.4569</v>
       </c>
       <c r="V4" t="n">
-        <v>153.1489</v>
+        <v>300.7776</v>
       </c>
       <c r="W4" t="n">
-        <v>311.3857</v>
+        <v>29.9639</v>
       </c>
       <c r="X4" t="n">
-        <v>538.0497</v>
+        <v>37.1034</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1557</v>
+        <v>44.1545</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.817500000000001</v>
+        <v>258.2477</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.5202</v>
+        <v>529.9868</v>
       </c>
       <c r="AB4" t="n">
-        <v>-8157.0557</v>
+        <v>907.4154</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5681.8236</v>
+        <v>25.1921</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3818.3092</v>
+        <v>32.5742</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0388</v>
+        <v>39.8586</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0546</v>
+        <v>149.5455</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0834</v>
+        <v>329.0244</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>599.2032</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>12.9688</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>19.4757</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>25.5004</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-8316.8315</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-5772.942</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-3793.6134</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.0809</v>
       </c>
     </row>
     <row r="5">
@@ -2593,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2608,76 +4324,106 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>181.6567</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>325.9343</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>567.191</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>26.4057</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>32.8497</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>40.1824</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>137.2623</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>347.0228</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>594.7768</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>21.5619</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>28.1895</v>
+        <v>186.2335</v>
       </c>
       <c r="U5" t="n">
-        <v>35.5545</v>
+        <v>355.1517</v>
       </c>
       <c r="V5" t="n">
-        <v>46.5271</v>
+        <v>627.9888999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>109.3437</v>
+        <v>28.7892</v>
       </c>
       <c r="X5" t="n">
-        <v>208.9375</v>
+        <v>36.4657</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.7029</v>
+        <v>44.3799</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.0666</v>
+        <v>81.5744</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.237</v>
+        <v>317.2566</v>
       </c>
       <c r="AB5" t="n">
-        <v>-558.0905</v>
+        <v>586.0945</v>
       </c>
       <c r="AC5" t="n">
-        <v>-186.5244</v>
+        <v>24.1019</v>
       </c>
       <c r="AD5" t="n">
-        <v>62.4151</v>
+        <v>31.6703</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0525</v>
+        <v>40.0258</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0732</v>
+        <v>46.8965</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.1147</v>
+        <v>109.9889</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>210.2574</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13.5281</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18.3106</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25.0148</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-237.9838</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5.5032</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>192.9619</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1066</v>
       </c>
     </row>
     <row r="6">
@@ -2700,91 +4446,121 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.273</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="G6" t="n">
         <v>0.0196</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0039</v>
+        <v>0.0136</v>
       </c>
       <c r="J6" t="n">
-        <v>230.9169</v>
+        <v>0.032</v>
       </c>
       <c r="K6" t="n">
-        <v>433.6542</v>
+        <v>0.0056</v>
       </c>
       <c r="L6" t="n">
-        <v>702.5907999999999</v>
+        <v>0.032</v>
       </c>
       <c r="M6" t="n">
-        <v>18.3584</v>
+        <v>0.0056</v>
       </c>
       <c r="N6" t="n">
-        <v>35.1977</v>
+        <v>0.035</v>
       </c>
       <c r="O6" t="n">
-        <v>56.0068</v>
+        <v>0.0058</v>
       </c>
       <c r="P6" t="n">
-        <v>16.5411</v>
+        <v>0.028</v>
       </c>
       <c r="Q6" t="n">
-        <v>245.2495</v>
+        <v>0.0052</v>
       </c>
       <c r="R6" t="n">
-        <v>498.1551</v>
+        <v>0.008</v>
       </c>
       <c r="S6" t="n">
-        <v>13.6714</v>
+        <v>0.0028</v>
       </c>
       <c r="T6" t="n">
-        <v>30.3559</v>
+        <v>244.0612</v>
       </c>
       <c r="U6" t="n">
-        <v>51.6694</v>
+        <v>461.3528</v>
       </c>
       <c r="V6" t="n">
-        <v>4.4633</v>
+        <v>779.4043</v>
       </c>
       <c r="W6" t="n">
-        <v>11.6259</v>
+        <v>17.7829</v>
       </c>
       <c r="X6" t="n">
-        <v>22.9392</v>
+        <v>33.4442</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.851</v>
+        <v>53.6941</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.6976</v>
+        <v>-42.7876</v>
       </c>
       <c r="AA6" t="n">
-        <v>36.1781</v>
+        <v>213.4914</v>
       </c>
       <c r="AB6" t="n">
-        <v>-654.1502</v>
+        <v>501.3288</v>
       </c>
       <c r="AC6" t="n">
-        <v>-383.8494</v>
+        <v>12.6791</v>
       </c>
       <c r="AD6" t="n">
-        <v>-179.9202</v>
+        <v>28.9971</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0577</v>
+        <v>49.3828</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.082</v>
+        <v>3.9905</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1311</v>
+        <v>10.8015</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23.0477</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.1774</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>15.7906</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34.5388</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-676.3836</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-351.3572</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-140.5143</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="7">
@@ -2807,91 +4583,121 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.585</v>
+        <v>0.335</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3264</v>
+        <v>0.0731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8932</v>
+        <v>0.5961</v>
       </c>
       <c r="J7" t="n">
-        <v>-90.9383</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>13.9943</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>108.8316</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>22.8177</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>31.8926</v>
+        <v>0.003</v>
       </c>
       <c r="O7" t="n">
-        <v>41.5047</v>
+        <v>0.0017</v>
       </c>
       <c r="P7" t="n">
-        <v>417.8372</v>
+        <v>0.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>668.9257</v>
+        <v>0.0133</v>
       </c>
       <c r="R7" t="n">
-        <v>1008.1514</v>
+        <v>0.84</v>
       </c>
       <c r="S7" t="n">
-        <v>18.1968</v>
+        <v>0.0116</v>
       </c>
       <c r="T7" t="n">
-        <v>27.257</v>
+        <v>-79.9738</v>
       </c>
       <c r="U7" t="n">
-        <v>37.0577</v>
+        <v>30.9806</v>
       </c>
       <c r="V7" t="n">
-        <v>234.9397</v>
+        <v>135.3182</v>
       </c>
       <c r="W7" t="n">
-        <v>436.5508</v>
+        <v>35.3904</v>
       </c>
       <c r="X7" t="n">
-        <v>682.2999</v>
+        <v>43.1718</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.7991</v>
+        <v>51.9758</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.447</v>
+        <v>368.6437</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.9011</v>
+        <v>651.0811</v>
       </c>
       <c r="AB7" t="n">
-        <v>-8630.2696</v>
+        <v>1011.3415</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6161.403</v>
+        <v>30.5084</v>
       </c>
       <c r="AD7" t="n">
-        <v>-4421.425</v>
+        <v>38.3708</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0316</v>
+        <v>47.6273</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0441</v>
+        <v>235.4412</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0648</v>
+        <v>448.1796</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>743.5761</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>16.9046</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25.3797</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34.0785</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-8592.205</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-6072.5382</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-4129.3348</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0619</v>
       </c>
     </row>
     <row r="8">
@@ -2914,91 +4720,121 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.63</v>
+        <v>0.801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3577</v>
+        <v>0.6327</v>
       </c>
       <c r="J8" t="n">
-        <v>324.7198</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>561.3892</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>854.5234</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>28.4296</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>40.7046</v>
+        <v>0.998</v>
       </c>
       <c r="O8" t="n">
-        <v>56.3795</v>
+        <v>0.0014</v>
       </c>
       <c r="P8" t="n">
-        <v>-9.1525</v>
+        <v>0.897</v>
       </c>
       <c r="Q8" t="n">
-        <v>299.1998</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>638.0936</v>
+        <v>0.332</v>
       </c>
       <c r="S8" t="n">
-        <v>23.5831</v>
+        <v>0.0149</v>
       </c>
       <c r="T8" t="n">
-        <v>36.1465</v>
+        <v>341.7722</v>
       </c>
       <c r="U8" t="n">
-        <v>51.8989</v>
+        <v>600.7388999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>963.6953999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>24.4032</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>38.899</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>55.664</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-82.76739999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>261.7674</v>
       </c>
       <c r="AB8" t="n">
-        <v>47.6288</v>
+        <v>623.1889</v>
       </c>
       <c r="AC8" t="n">
-        <v>86.0308</v>
+        <v>19.7361</v>
       </c>
       <c r="AD8" t="n">
-        <v>133.3441</v>
+        <v>34.284</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0567</v>
+        <v>51.1089</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.1287</v>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>47.8621</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>86.42789999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>133.2455</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="9">
@@ -3036,76 +4872,106 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>11.6214</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>163.8447</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>347.1019</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>87.6808</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>128.5711</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>182.2862</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>294.6986</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>671.7824000000001</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1204.8906</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>82.91249999999999</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>123.3485</v>
+        <v>2.6855</v>
       </c>
       <c r="U9" t="n">
-        <v>176.2527</v>
+        <v>156.5033</v>
       </c>
       <c r="V9" t="n">
-        <v>29.1705</v>
+        <v>338.9064</v>
       </c>
       <c r="W9" t="n">
-        <v>397.4199</v>
+        <v>87.7835</v>
       </c>
       <c r="X9" t="n">
-        <v>792.6673</v>
+        <v>127.3507</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.8287</v>
+        <v>182.1587</v>
       </c>
       <c r="Z9" t="n">
-        <v>86.5689</v>
+        <v>296.6047</v>
       </c>
       <c r="AA9" t="n">
-        <v>142.6292</v>
+        <v>695.8787</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6822.0958</v>
+        <v>1179.0994</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4522.5369</v>
+        <v>82.9669</v>
       </c>
       <c r="AD9" t="n">
-        <v>-3074.0365</v>
+        <v>122.7105</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0134</v>
+        <v>177.4923</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0189</v>
+        <v>87.3582</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0265</v>
+        <v>446.422</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>878.1552</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>46.7107</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>87.86750000000001</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>143.4038</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-6728.1585</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-4554.7262</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-2881.4567</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="10">
@@ -3128,91 +4994,121 @@
         <v>0.999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.979</v>
+        <v>0.983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.068</v>
+        <v>0.054</v>
       </c>
       <c r="G10" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0277</v>
+        <v>0.0101</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1077</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>98.423</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>244.2065</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>419.437</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>48.9076</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>61.8977</v>
+        <v>0.002</v>
       </c>
       <c r="O10" t="n">
-        <v>77.1735</v>
+        <v>0.0014</v>
       </c>
       <c r="P10" t="n">
-        <v>287.2874</v>
+        <v>0.049</v>
       </c>
       <c r="Q10" t="n">
-        <v>601.0382</v>
+        <v>0.0068</v>
       </c>
       <c r="R10" t="n">
-        <v>1003.7764</v>
+        <v>0.123</v>
       </c>
       <c r="S10" t="n">
-        <v>43.6281</v>
+        <v>0.0104</v>
       </c>
       <c r="T10" t="n">
-        <v>56.9991</v>
+        <v>100.9145</v>
       </c>
       <c r="U10" t="n">
-        <v>72.3762</v>
+        <v>265.3826</v>
       </c>
       <c r="V10" t="n">
-        <v>143.3783</v>
+        <v>460.3501</v>
       </c>
       <c r="W10" t="n">
-        <v>315.0816</v>
+        <v>56.269</v>
       </c>
       <c r="X10" t="n">
-        <v>536.5626</v>
+        <v>69.34050000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.9239</v>
+        <v>84.6101</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.9955</v>
+        <v>276.4458</v>
       </c>
       <c r="AA10" t="n">
-        <v>31.5004</v>
+        <v>580.8769</v>
       </c>
       <c r="AB10" t="n">
-        <v>-7021.2205</v>
+        <v>1014.1145</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4763.4307</v>
+        <v>50.8512</v>
       </c>
       <c r="AD10" t="n">
-        <v>-2886.8372</v>
+        <v>64.3416</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0405</v>
+        <v>80.48520000000001</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0571</v>
+        <v>157.0369</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0867</v>
+        <v>330.4875</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>576.3142</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>21.2154</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>30.1156</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40.2426</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-6973.2678</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-4653.7604</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-2920.872</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.0878</v>
       </c>
     </row>
     <row r="11">
@@ -3235,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.343</v>
+        <v>0.626</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3250,76 +5146,106 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>222.7524</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>426.9179</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>686.929</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>50.9766</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>64.74720000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>81.6289</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>132.8906</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>423.8915</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>773.7919000000001</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>45.8001</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>59.9483</v>
+        <v>246.6036</v>
       </c>
       <c r="U11" t="n">
-        <v>77.0566</v>
+        <v>463.8539</v>
       </c>
       <c r="V11" t="n">
-        <v>65.2076</v>
+        <v>767.8787</v>
       </c>
       <c r="W11" t="n">
-        <v>127.774</v>
+        <v>52.2029</v>
       </c>
       <c r="X11" t="n">
-        <v>231.3319</v>
+        <v>67.77760000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.1726</v>
+        <v>86.2132</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.1346</v>
+        <v>73.6125</v>
       </c>
       <c r="AA11" t="n">
-        <v>33.9641</v>
+        <v>393.1179</v>
       </c>
       <c r="AB11" t="n">
-        <v>-633.9299</v>
+        <v>742.2267000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>-251.5936</v>
+        <v>47.2349</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4644</v>
+        <v>63.0301</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0505</v>
+        <v>81.1733</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.07240000000000001</v>
+        <v>62.4901</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1091</v>
+        <v>129.1946</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>242.0853</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>19.3739</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>28.0848</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>39.0364</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-285.2392</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-31.0423</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>169.4204</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.1072</v>
       </c>
     </row>
     <row r="12">
@@ -3357,76 +5283,106 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>305.8662</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>544.4965999999999</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>838.3368</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>52.2652</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>78.1871</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>115.1956</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4308</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>314.1418</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>664.0700000000001</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>47.5699</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>73.1922</v>
+        <v>323.8761</v>
       </c>
       <c r="U12" t="n">
-        <v>109.61</v>
+        <v>587.6301</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8679</v>
+        <v>948.1161</v>
       </c>
       <c r="W12" t="n">
-        <v>13.8895</v>
+        <v>47.0973</v>
       </c>
       <c r="X12" t="n">
-        <v>27.5116</v>
+        <v>74.081</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.4307</v>
+        <v>111.4085</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.5728</v>
+        <v>-70.09690000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>71.67359999999999</v>
+        <v>274.4564</v>
       </c>
       <c r="AB12" t="n">
-        <v>-895.6872</v>
+        <v>644.4358</v>
       </c>
       <c r="AC12" t="n">
-        <v>-493.9176</v>
+        <v>42.4146</v>
       </c>
       <c r="AD12" t="n">
-        <v>-233.488</v>
+        <v>69.46550000000001</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0567</v>
+        <v>107.035</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.082</v>
+        <v>5.1272</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1287</v>
+        <v>13.1656</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27.4983</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>13.2913</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>34.4248</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70.0063</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-885.9485</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-454.6549</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-189.0601</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="13">
@@ -3452,88 +5408,118 @@
         <v>0.999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.302</v>
+        <v>0.145</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0605</v>
+        <v>0.0101</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5346</v>
+        <v>0.2712</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.5763</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>112.0111</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>238.3842</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>55.3038</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>69.4335</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>86.6751</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>426.4121</v>
+        <v>0.054</v>
       </c>
       <c r="Q13" t="n">
-        <v>734.4619</v>
+        <v>0.0071</v>
       </c>
       <c r="R13" t="n">
-        <v>1146.3236</v>
+        <v>0.545</v>
       </c>
       <c r="S13" t="n">
-        <v>50.4451</v>
+        <v>0.0157</v>
       </c>
       <c r="T13" t="n">
-        <v>64.8188</v>
+        <v>8.603</v>
       </c>
       <c r="U13" t="n">
-        <v>82.02760000000001</v>
+        <v>131.2162</v>
       </c>
       <c r="V13" t="n">
-        <v>249.8288</v>
+        <v>272.2416</v>
       </c>
       <c r="W13" t="n">
-        <v>450.2174</v>
+        <v>66.02500000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>691.9383</v>
+        <v>79.9331</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.1562</v>
+        <v>96.5445</v>
       </c>
       <c r="Z13" t="n">
-        <v>28.1266</v>
+        <v>417.0237</v>
       </c>
       <c r="AA13" t="n">
-        <v>44.0765</v>
+        <v>713.928</v>
       </c>
       <c r="AB13" t="n">
-        <v>-7548.8836</v>
+        <v>1141.866</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5275.5785</v>
+        <v>61.4473</v>
       </c>
       <c r="AD13" t="n">
-        <v>-3484.317</v>
+        <v>75.2101</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0326</v>
+        <v>91.91540000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.045</v>
+        <v>262.8833</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.06660000000000001</v>
+        <v>464.4497</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>760.0542</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>27.7005</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>40.6695</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>55.0824</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-7245.629</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-5018.041</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-3230.6396</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3556,91 +5542,121 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="F14" t="n">
-        <v>0.287</v>
+        <v>0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9216</v>
+        <v>0.9804</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4334</v>
+        <v>0.7833</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0524</v>
+        <v>0.2524</v>
       </c>
       <c r="J14" t="n">
-        <v>246.3381</v>
+        <v>0.965</v>
       </c>
       <c r="K14" t="n">
-        <v>443.768</v>
+        <v>0.0058</v>
       </c>
       <c r="L14" t="n">
-        <v>713.5906</v>
+        <v>0.965</v>
       </c>
       <c r="M14" t="n">
-        <v>13.1844</v>
+        <v>0.0058</v>
       </c>
       <c r="N14" t="n">
-        <v>18.5342</v>
+        <v>0.929</v>
       </c>
       <c r="O14" t="n">
-        <v>24.0167</v>
+        <v>0.0081</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8567</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>234.4638</v>
+        <v>0.0157</v>
       </c>
       <c r="R14" t="n">
-        <v>478.4843</v>
+        <v>0.079</v>
       </c>
       <c r="S14" t="n">
-        <v>8.506600000000001</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>14.0447</v>
+        <v>260.2313</v>
       </c>
       <c r="U14" t="n">
-        <v>19.4774</v>
+        <v>473.4537</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>789.3863</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>11.0104</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>17.8314</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>23.7686</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-47.8277</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>200.9614</v>
       </c>
       <c r="AB14" t="n">
-        <v>49.2936</v>
+        <v>483.4878</v>
       </c>
       <c r="AC14" t="n">
-        <v>87.13500000000001</v>
+        <v>6.4758</v>
       </c>
       <c r="AD14" t="n">
-        <v>137.2735</v>
+        <v>13.3336</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0577</v>
+        <v>19.1865</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1311</v>
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50.297</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>87.25320000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>138.0239</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="15">
@@ -3660,94 +5676,124 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.95</v>
+        <v>0.948</v>
       </c>
       <c r="E15" t="n">
-        <v>0.044</v>
+        <v>0.148</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004</v>
+        <v>0.034</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0078</v>
+        <v>0.0261</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0019</v>
+        <v>0.0466</v>
       </c>
       <c r="J15" t="n">
-        <v>33.792</v>
+        <v>0.003</v>
       </c>
       <c r="K15" t="n">
-        <v>201.4027</v>
+        <v>0.0017</v>
       </c>
       <c r="L15" t="n">
-        <v>398.9821</v>
+        <v>0.003</v>
       </c>
       <c r="M15" t="n">
-        <v>32.9201</v>
+        <v>0.0017</v>
       </c>
       <c r="N15" t="n">
-        <v>54.6282</v>
+        <v>0.017</v>
       </c>
       <c r="O15" t="n">
-        <v>76.25149999999999</v>
+        <v>0.0041</v>
       </c>
       <c r="P15" t="n">
-        <v>121.5295</v>
+        <v>0.039</v>
       </c>
       <c r="Q15" t="n">
-        <v>481.8229</v>
+        <v>0.0061</v>
       </c>
       <c r="R15" t="n">
-        <v>880.0793</v>
+        <v>0.026</v>
       </c>
       <c r="S15" t="n">
-        <v>28.8776</v>
+        <v>0.005</v>
       </c>
       <c r="T15" t="n">
-        <v>49.7468</v>
+        <v>32.0236</v>
       </c>
       <c r="U15" t="n">
-        <v>71.6972</v>
+        <v>198.8733</v>
       </c>
       <c r="V15" t="n">
-        <v>-85.7073</v>
+        <v>407.6857</v>
       </c>
       <c r="W15" t="n">
-        <v>242.1789</v>
+        <v>33.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>591.9087</v>
+        <v>53.6771</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.3887</v>
+        <v>75.95829999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>35.6789</v>
+        <v>101.4053</v>
       </c>
       <c r="AA15" t="n">
-        <v>59.524</v>
+        <v>493.8181</v>
       </c>
       <c r="AB15" t="n">
-        <v>-7576.136</v>
+        <v>899.9864</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5178.3622</v>
+        <v>27.936</v>
       </c>
       <c r="AD15" t="n">
-        <v>-3475.005</v>
+        <v>49.11</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0137</v>
+        <v>71.1116</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0189</v>
+        <v>-75.4547</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0275</v>
+        <v>272.5886</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>677.4353</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>14.6323</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>36.1389</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>58.2405</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-7767.744</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-5200.1019</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-3467.9598</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.0267</v>
       </c>
     </row>
     <row r="16">
@@ -3770,91 +5816,121 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.105</v>
+        <v>0.075</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1932</v>
+        <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0485</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.0382</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>129.9706</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>267.7732</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19.8853</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>28.5365</v>
+        <v>0.016</v>
       </c>
       <c r="O16" t="n">
-        <v>36.7816</v>
+        <v>0.004</v>
       </c>
       <c r="P16" t="n">
-        <v>306.4469</v>
+        <v>0.146</v>
       </c>
       <c r="Q16" t="n">
-        <v>552.4836</v>
+        <v>0.0112</v>
       </c>
       <c r="R16" t="n">
-        <v>886.1239</v>
+        <v>0.047</v>
       </c>
       <c r="S16" t="n">
-        <v>15.1516</v>
+        <v>0.0067</v>
       </c>
       <c r="T16" t="n">
-        <v>23.708</v>
+        <v>0.9105</v>
       </c>
       <c r="U16" t="n">
-        <v>32.3943</v>
+        <v>142.4569</v>
       </c>
       <c r="V16" t="n">
-        <v>153.1489</v>
+        <v>300.7776</v>
       </c>
       <c r="W16" t="n">
-        <v>311.3857</v>
+        <v>29.9639</v>
       </c>
       <c r="X16" t="n">
-        <v>538.0497</v>
+        <v>37.1034</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1557</v>
+        <v>44.1545</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.817500000000001</v>
+        <v>258.2477</v>
       </c>
       <c r="AA16" t="n">
-        <v>17.5202</v>
+        <v>529.9868</v>
       </c>
       <c r="AB16" t="n">
-        <v>-8157.0557</v>
+        <v>907.4154</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5681.8236</v>
+        <v>25.1921</v>
       </c>
       <c r="AD16" t="n">
-        <v>-3818.3092</v>
+        <v>32.5742</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0388</v>
+        <v>39.8586</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0546</v>
+        <v>149.5455</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0834</v>
+        <v>329.0244</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>599.2032</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>12.9688</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>19.4757</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25.5004</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-8316.8315</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-5772.942</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-3793.6134</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.0809</v>
       </c>
     </row>
     <row r="17">
@@ -3877,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -3892,76 +5968,106 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>181.6567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>325.9343</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>567.191</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>26.4057</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>32.8497</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>40.1824</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>137.2623</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>347.0228</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>594.7768</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>21.5619</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28.1895</v>
+        <v>186.2335</v>
       </c>
       <c r="U17" t="n">
-        <v>35.5545</v>
+        <v>355.1517</v>
       </c>
       <c r="V17" t="n">
-        <v>46.5271</v>
+        <v>627.9888999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>109.3437</v>
+        <v>28.7892</v>
       </c>
       <c r="X17" t="n">
-        <v>208.9375</v>
+        <v>36.4657</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.7029</v>
+        <v>44.3799</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.0666</v>
+        <v>81.5744</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.237</v>
+        <v>317.2566</v>
       </c>
       <c r="AB17" t="n">
-        <v>-558.0905</v>
+        <v>586.0945</v>
       </c>
       <c r="AC17" t="n">
-        <v>-186.5244</v>
+        <v>24.1019</v>
       </c>
       <c r="AD17" t="n">
-        <v>62.4151</v>
+        <v>31.6703</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0525</v>
+        <v>40.0258</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0732</v>
+        <v>46.8965</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1147</v>
+        <v>109.9889</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>210.2574</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>13.5281</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>18.3106</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25.0148</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-237.9838</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>5.5032</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>192.9619</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.1066</v>
       </c>
     </row>
     <row r="18">
@@ -3984,91 +6090,121 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.273</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="G18" t="n">
         <v>0.0196</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0039</v>
+        <v>0.0136</v>
       </c>
       <c r="J18" t="n">
-        <v>230.9169</v>
+        <v>0.032</v>
       </c>
       <c r="K18" t="n">
-        <v>433.6542</v>
+        <v>0.0056</v>
       </c>
       <c r="L18" t="n">
-        <v>702.5907999999999</v>
+        <v>0.032</v>
       </c>
       <c r="M18" t="n">
-        <v>18.3584</v>
+        <v>0.0056</v>
       </c>
       <c r="N18" t="n">
-        <v>35.1977</v>
+        <v>0.035</v>
       </c>
       <c r="O18" t="n">
-        <v>56.0068</v>
+        <v>0.0058</v>
       </c>
       <c r="P18" t="n">
-        <v>16.5411</v>
+        <v>0.028</v>
       </c>
       <c r="Q18" t="n">
-        <v>245.2495</v>
+        <v>0.0052</v>
       </c>
       <c r="R18" t="n">
-        <v>498.1551</v>
+        <v>0.008</v>
       </c>
       <c r="S18" t="n">
-        <v>13.6714</v>
+        <v>0.0028</v>
       </c>
       <c r="T18" t="n">
-        <v>30.3559</v>
+        <v>244.0612</v>
       </c>
       <c r="U18" t="n">
-        <v>51.6694</v>
+        <v>461.3528</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4633</v>
+        <v>779.4043</v>
       </c>
       <c r="W18" t="n">
-        <v>11.6259</v>
+        <v>17.7829</v>
       </c>
       <c r="X18" t="n">
-        <v>22.9392</v>
+        <v>33.4442</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.851</v>
+        <v>53.6941</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.6976</v>
+        <v>-42.7876</v>
       </c>
       <c r="AA18" t="n">
-        <v>36.1781</v>
+        <v>213.4914</v>
       </c>
       <c r="AB18" t="n">
-        <v>-654.1502</v>
+        <v>501.3288</v>
       </c>
       <c r="AC18" t="n">
-        <v>-383.8494</v>
+        <v>12.6791</v>
       </c>
       <c r="AD18" t="n">
-        <v>-179.9202</v>
+        <v>28.9971</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0577</v>
+        <v>49.3828</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.082</v>
+        <v>3.9905</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1311</v>
+        <v>10.8015</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23.0477</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.1774</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>15.7906</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34.5388</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-676.3836</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-351.3572</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-140.5143</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="19">
@@ -4091,91 +6227,121 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="F19" t="n">
-        <v>0.585</v>
+        <v>0.335</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3264</v>
+        <v>0.0731</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8932</v>
+        <v>0.5961</v>
       </c>
       <c r="J19" t="n">
-        <v>-90.9383</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>13.9943</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>108.8316</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>22.8177</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>31.8926</v>
+        <v>0.003</v>
       </c>
       <c r="O19" t="n">
-        <v>41.5047</v>
+        <v>0.0017</v>
       </c>
       <c r="P19" t="n">
-        <v>417.8372</v>
+        <v>0.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>668.9257</v>
+        <v>0.0133</v>
       </c>
       <c r="R19" t="n">
-        <v>1008.1514</v>
+        <v>0.84</v>
       </c>
       <c r="S19" t="n">
-        <v>18.1968</v>
+        <v>0.0116</v>
       </c>
       <c r="T19" t="n">
-        <v>27.257</v>
+        <v>-79.9738</v>
       </c>
       <c r="U19" t="n">
-        <v>37.0577</v>
+        <v>30.9806</v>
       </c>
       <c r="V19" t="n">
-        <v>234.9397</v>
+        <v>135.3182</v>
       </c>
       <c r="W19" t="n">
-        <v>436.5508</v>
+        <v>35.3904</v>
       </c>
       <c r="X19" t="n">
-        <v>682.2999</v>
+        <v>43.1718</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.7991</v>
+        <v>51.9758</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.447</v>
+        <v>368.6437</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.9011</v>
+        <v>651.0811</v>
       </c>
       <c r="AB19" t="n">
-        <v>-8630.2696</v>
+        <v>1011.3415</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6161.403</v>
+        <v>30.5084</v>
       </c>
       <c r="AD19" t="n">
-        <v>-4421.425</v>
+        <v>38.3708</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.0316</v>
+        <v>47.6273</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0441</v>
+        <v>235.4412</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0648</v>
+        <v>448.1796</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>743.5761</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>16.9046</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>25.3797</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34.0785</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-8592.205</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-6072.5382</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-4129.3348</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.0619</v>
       </c>
     </row>
     <row r="20">
@@ -4198,91 +6364,121 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.63</v>
+        <v>0.801</v>
       </c>
       <c r="G20" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3577</v>
+        <v>0.6327</v>
       </c>
       <c r="J20" t="n">
-        <v>324.7198</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>561.3892</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>854.5234</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>28.4296</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40.7046</v>
+        <v>0.998</v>
       </c>
       <c r="O20" t="n">
-        <v>56.3795</v>
+        <v>0.0014</v>
       </c>
       <c r="P20" t="n">
-        <v>-9.1525</v>
+        <v>0.897</v>
       </c>
       <c r="Q20" t="n">
-        <v>299.1998</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>638.0936</v>
+        <v>0.332</v>
       </c>
       <c r="S20" t="n">
-        <v>23.5831</v>
+        <v>0.0149</v>
       </c>
       <c r="T20" t="n">
-        <v>36.1465</v>
+        <v>341.7722</v>
       </c>
       <c r="U20" t="n">
-        <v>51.8989</v>
+        <v>600.7388999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>963.6953999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>24.4032</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>38.899</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>55.664</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-82.76739999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>261.7674</v>
       </c>
       <c r="AB20" t="n">
-        <v>47.6288</v>
+        <v>623.1889</v>
       </c>
       <c r="AC20" t="n">
-        <v>86.0308</v>
+        <v>19.7361</v>
       </c>
       <c r="AD20" t="n">
-        <v>133.3441</v>
+        <v>34.284</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0567</v>
+        <v>51.1089</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.1287</v>
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>47.8621</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>86.42789999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>133.2455</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="21">
@@ -4320,76 +6516,106 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>11.6214</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>163.8447</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>347.1019</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>87.6808</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>128.5711</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>182.2862</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>294.6986</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>671.7824000000001</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1204.8906</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>82.91249999999999</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>123.3485</v>
+        <v>2.6855</v>
       </c>
       <c r="U21" t="n">
-        <v>176.2527</v>
+        <v>156.5033</v>
       </c>
       <c r="V21" t="n">
-        <v>29.1705</v>
+        <v>338.9064</v>
       </c>
       <c r="W21" t="n">
-        <v>397.4199</v>
+        <v>87.7835</v>
       </c>
       <c r="X21" t="n">
-        <v>792.6673</v>
+        <v>127.3507</v>
       </c>
       <c r="Y21" t="n">
-        <v>45.8287</v>
+        <v>182.1587</v>
       </c>
       <c r="Z21" t="n">
-        <v>86.5689</v>
+        <v>296.6047</v>
       </c>
       <c r="AA21" t="n">
-        <v>142.6292</v>
+        <v>695.8787</v>
       </c>
       <c r="AB21" t="n">
-        <v>-6822.0958</v>
+        <v>1179.0994</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4522.5369</v>
+        <v>82.9669</v>
       </c>
       <c r="AD21" t="n">
-        <v>-3074.0365</v>
+        <v>122.7105</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.0134</v>
+        <v>177.4923</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0189</v>
+        <v>87.3582</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0265</v>
+        <v>446.422</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>878.1552</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>46.7107</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>87.86750000000001</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>143.4038</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-6728.1585</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-4554.7262</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-2881.4567</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="22">
@@ -4412,91 +6638,121 @@
         <v>0.999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.979</v>
+        <v>0.983</v>
       </c>
       <c r="F22" t="n">
-        <v>0.068</v>
+        <v>0.054</v>
       </c>
       <c r="G22" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0277</v>
+        <v>0.0101</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1077</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>98.423</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>244.2065</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>419.437</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>48.9076</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>61.8977</v>
+        <v>0.002</v>
       </c>
       <c r="O22" t="n">
-        <v>77.1735</v>
+        <v>0.0014</v>
       </c>
       <c r="P22" t="n">
-        <v>287.2874</v>
+        <v>0.049</v>
       </c>
       <c r="Q22" t="n">
-        <v>601.0382</v>
+        <v>0.0068</v>
       </c>
       <c r="R22" t="n">
-        <v>1003.7764</v>
+        <v>0.123</v>
       </c>
       <c r="S22" t="n">
-        <v>43.6281</v>
+        <v>0.0104</v>
       </c>
       <c r="T22" t="n">
-        <v>56.9991</v>
+        <v>100.9145</v>
       </c>
       <c r="U22" t="n">
-        <v>72.3762</v>
+        <v>265.3826</v>
       </c>
       <c r="V22" t="n">
-        <v>143.3783</v>
+        <v>460.3501</v>
       </c>
       <c r="W22" t="n">
-        <v>315.0816</v>
+        <v>56.269</v>
       </c>
       <c r="X22" t="n">
-        <v>536.5626</v>
+        <v>69.34050000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.9239</v>
+        <v>84.6101</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.9955</v>
+        <v>276.4458</v>
       </c>
       <c r="AA22" t="n">
-        <v>31.5004</v>
+        <v>580.8769</v>
       </c>
       <c r="AB22" t="n">
-        <v>-7021.2205</v>
+        <v>1014.1145</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4763.4307</v>
+        <v>50.8512</v>
       </c>
       <c r="AD22" t="n">
-        <v>-2886.8372</v>
+        <v>64.3416</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.0405</v>
+        <v>80.48520000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0571</v>
+        <v>157.0369</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.0867</v>
+        <v>330.4875</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>576.3142</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>21.2154</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>30.1156</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>40.2426</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-6973.2678</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-4653.7604</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-2920.872</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.0878</v>
       </c>
     </row>
     <row r="23">
@@ -4519,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.343</v>
+        <v>0.626</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -4534,76 +6790,106 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>222.7524</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>426.9179</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>686.929</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>50.9766</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>64.74720000000001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>81.6289</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>132.8906</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>423.8915</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>773.7919000000001</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>45.8001</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>59.9483</v>
+        <v>246.6036</v>
       </c>
       <c r="U23" t="n">
-        <v>77.0566</v>
+        <v>463.8539</v>
       </c>
       <c r="V23" t="n">
-        <v>65.2076</v>
+        <v>767.8787</v>
       </c>
       <c r="W23" t="n">
-        <v>127.774</v>
+        <v>52.2029</v>
       </c>
       <c r="X23" t="n">
-        <v>231.3319</v>
+        <v>67.77760000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>15.1726</v>
+        <v>86.2132</v>
       </c>
       <c r="Z23" t="n">
-        <v>23.1346</v>
+        <v>73.6125</v>
       </c>
       <c r="AA23" t="n">
-        <v>33.9641</v>
+        <v>393.1179</v>
       </c>
       <c r="AB23" t="n">
-        <v>-633.9299</v>
+        <v>742.2267000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-251.5936</v>
+        <v>47.2349</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4644</v>
+        <v>63.0301</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0505</v>
+        <v>81.1733</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.07240000000000001</v>
+        <v>62.4901</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1091</v>
+        <v>129.1946</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>242.0853</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>19.3739</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>28.0848</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>39.0364</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-285.2392</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-31.0423</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>169.4204</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.1072</v>
       </c>
     </row>
     <row r="24">
@@ -4641,76 +6927,106 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>305.8662</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>544.4965999999999</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>838.3368</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>52.2652</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>78.1871</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>115.1956</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4308</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>314.1418</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>664.0700000000001</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>47.5699</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>73.1922</v>
+        <v>323.8761</v>
       </c>
       <c r="U24" t="n">
-        <v>109.61</v>
+        <v>587.6301</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8679</v>
+        <v>948.1161</v>
       </c>
       <c r="W24" t="n">
-        <v>13.8895</v>
+        <v>47.0973</v>
       </c>
       <c r="X24" t="n">
-        <v>27.5116</v>
+        <v>74.081</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.4307</v>
+        <v>111.4085</v>
       </c>
       <c r="Z24" t="n">
-        <v>36.5728</v>
+        <v>-70.09690000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>71.67359999999999</v>
+        <v>274.4564</v>
       </c>
       <c r="AB24" t="n">
-        <v>-895.6872</v>
+        <v>644.4358</v>
       </c>
       <c r="AC24" t="n">
-        <v>-493.9176</v>
+        <v>42.4146</v>
       </c>
       <c r="AD24" t="n">
-        <v>-233.488</v>
+        <v>69.46550000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0567</v>
+        <v>107.035</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.082</v>
+        <v>5.1272</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.1287</v>
+        <v>13.1656</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>27.4983</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>13.2913</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>34.4248</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>70.0063</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-885.9485</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-454.6549</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-189.0601</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="25">
@@ -4736,88 +7052,118 @@
         <v>0.999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.302</v>
+        <v>0.145</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0605</v>
+        <v>0.0101</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5346</v>
+        <v>0.2712</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5763</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>112.0111</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>238.3842</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>55.3038</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>69.4335</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>86.6751</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>426.4121</v>
+        <v>0.054</v>
       </c>
       <c r="Q25" t="n">
-        <v>734.4619</v>
+        <v>0.0071</v>
       </c>
       <c r="R25" t="n">
-        <v>1146.3236</v>
+        <v>0.545</v>
       </c>
       <c r="S25" t="n">
-        <v>50.4451</v>
+        <v>0.0157</v>
       </c>
       <c r="T25" t="n">
-        <v>64.8188</v>
+        <v>8.603</v>
       </c>
       <c r="U25" t="n">
-        <v>82.02760000000001</v>
+        <v>131.2162</v>
       </c>
       <c r="V25" t="n">
-        <v>249.8288</v>
+        <v>272.2416</v>
       </c>
       <c r="W25" t="n">
-        <v>450.2174</v>
+        <v>66.02500000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>691.9383</v>
+        <v>79.9331</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.1562</v>
+        <v>96.5445</v>
       </c>
       <c r="Z25" t="n">
-        <v>28.1266</v>
+        <v>417.0237</v>
       </c>
       <c r="AA25" t="n">
-        <v>44.0765</v>
+        <v>713.928</v>
       </c>
       <c r="AB25" t="n">
-        <v>-7548.8836</v>
+        <v>1141.866</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5275.5785</v>
+        <v>61.4473</v>
       </c>
       <c r="AD25" t="n">
-        <v>-3484.317</v>
+        <v>75.2101</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.0326</v>
+        <v>91.91540000000001</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.045</v>
+        <v>262.8833</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.06660000000000001</v>
+        <v>464.4497</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>760.0542</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>27.7005</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>40.6695</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>55.0824</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-7245.629</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-5018.041</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-3230.6396</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -4840,91 +7186,121 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.916</v>
+        <v>0.949</v>
       </c>
       <c r="F26" t="n">
-        <v>0.207</v>
+        <v>0.273</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8922</v>
+        <v>0.9412</v>
       </c>
       <c r="H26" t="n">
-        <v>0.282</v>
+        <v>0.4178</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0155</v>
+        <v>0.033</v>
       </c>
       <c r="J26" t="n">
-        <v>246.3381</v>
+        <v>0.949</v>
       </c>
       <c r="K26" t="n">
-        <v>443.768</v>
+        <v>0.007</v>
       </c>
       <c r="L26" t="n">
-        <v>713.5906</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>13.1844</v>
+        <v>0.0075</v>
       </c>
       <c r="N26" t="n">
-        <v>18.5342</v>
+        <v>0.536</v>
       </c>
       <c r="O26" t="n">
-        <v>24.0167</v>
+        <v>0.0158</v>
       </c>
       <c r="P26" t="n">
-        <v>7.8567</v>
+        <v>0.125</v>
       </c>
       <c r="Q26" t="n">
-        <v>234.4638</v>
+        <v>0.0105</v>
       </c>
       <c r="R26" t="n">
-        <v>478.4843</v>
+        <v>0.004</v>
       </c>
       <c r="S26" t="n">
-        <v>8.506600000000001</v>
+        <v>0.002</v>
       </c>
       <c r="T26" t="n">
-        <v>14.0447</v>
+        <v>260.2313</v>
       </c>
       <c r="U26" t="n">
-        <v>19.4774</v>
+        <v>473.4537</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>789.3863</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>11.0104</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>17.8314</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>23.7686</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>-47.8277</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>200.9614</v>
       </c>
       <c r="AB26" t="n">
-        <v>49.2936</v>
+        <v>483.4878</v>
       </c>
       <c r="AC26" t="n">
-        <v>87.13500000000001</v>
+        <v>6.4758</v>
       </c>
       <c r="AD26" t="n">
-        <v>137.2735</v>
+        <v>13.3336</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0577</v>
+        <v>19.1865</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.1311</v>
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>50.297</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>87.25320000000001</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>138.0239</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="27">
@@ -4944,13 +7320,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.95</v>
+        <v>0.948</v>
       </c>
       <c r="E27" t="n">
-        <v>0.043</v>
+        <v>0.117</v>
       </c>
       <c r="F27" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4959,79 +7335,109 @@
         <v>0.0078</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0019</v>
+        <v>0.0252</v>
       </c>
       <c r="J27" t="n">
-        <v>33.792</v>
+        <v>0.003</v>
       </c>
       <c r="K27" t="n">
-        <v>201.4027</v>
+        <v>0.0017</v>
       </c>
       <c r="L27" t="n">
-        <v>398.9821</v>
+        <v>0.003</v>
       </c>
       <c r="M27" t="n">
-        <v>32.9201</v>
+        <v>0.0017</v>
       </c>
       <c r="N27" t="n">
-        <v>54.6282</v>
+        <v>0.011</v>
       </c>
       <c r="O27" t="n">
-        <v>76.25149999999999</v>
+        <v>0.0033</v>
       </c>
       <c r="P27" t="n">
-        <v>121.5295</v>
+        <v>0.022</v>
       </c>
       <c r="Q27" t="n">
-        <v>481.8229</v>
+        <v>0.0046</v>
       </c>
       <c r="R27" t="n">
-        <v>880.0793</v>
+        <v>0.011</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8776</v>
+        <v>0.0033</v>
       </c>
       <c r="T27" t="n">
-        <v>49.7468</v>
+        <v>32.0236</v>
       </c>
       <c r="U27" t="n">
-        <v>71.6972</v>
+        <v>198.8733</v>
       </c>
       <c r="V27" t="n">
-        <v>-85.7073</v>
+        <v>407.6857</v>
       </c>
       <c r="W27" t="n">
-        <v>242.1789</v>
+        <v>33.1952</v>
       </c>
       <c r="X27" t="n">
-        <v>591.9087</v>
+        <v>53.6771</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.3887</v>
+        <v>75.95829999999999</v>
       </c>
       <c r="Z27" t="n">
-        <v>35.6789</v>
+        <v>101.4053</v>
       </c>
       <c r="AA27" t="n">
-        <v>59.524</v>
+        <v>493.8181</v>
       </c>
       <c r="AB27" t="n">
-        <v>-7576.136</v>
+        <v>899.9864</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5178.3622</v>
+        <v>27.936</v>
       </c>
       <c r="AD27" t="n">
-        <v>-3475.005</v>
+        <v>49.11</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.0137</v>
+        <v>71.1116</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0189</v>
+        <v>-75.4547</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.0275</v>
+        <v>272.5886</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>677.4353</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>14.6323</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36.1389</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>58.2405</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-7767.744</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-5200.1019</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-3467.9598</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.0267</v>
       </c>
     </row>
     <row r="28">
@@ -5054,91 +7460,121 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.944</v>
+        <v>0.928</v>
       </c>
       <c r="F28" t="n">
-        <v>0.103</v>
+        <v>0.015</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1906</v>
+        <v>0.0183</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0466</v>
+        <v>0.0155</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.0382</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>129.9706</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>267.7732</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>19.8853</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>28.5365</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>36.7816</v>
+        <v>0.003</v>
       </c>
       <c r="P28" t="n">
-        <v>306.4469</v>
+        <v>0.039</v>
       </c>
       <c r="Q28" t="n">
-        <v>552.4836</v>
+        <v>0.0061</v>
       </c>
       <c r="R28" t="n">
-        <v>886.1239</v>
+        <v>0.003</v>
       </c>
       <c r="S28" t="n">
-        <v>15.1516</v>
+        <v>0.0017</v>
       </c>
       <c r="T28" t="n">
-        <v>23.708</v>
+        <v>0.9105</v>
       </c>
       <c r="U28" t="n">
-        <v>32.3943</v>
+        <v>142.4569</v>
       </c>
       <c r="V28" t="n">
-        <v>153.1489</v>
+        <v>300.7776</v>
       </c>
       <c r="W28" t="n">
-        <v>311.3857</v>
+        <v>29.9639</v>
       </c>
       <c r="X28" t="n">
-        <v>538.0497</v>
+        <v>37.1034</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1557</v>
+        <v>44.1545</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.817500000000001</v>
+        <v>258.2477</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.5202</v>
+        <v>529.9868</v>
       </c>
       <c r="AB28" t="n">
-        <v>-8157.0557</v>
+        <v>907.4154</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5681.8236</v>
+        <v>25.1921</v>
       </c>
       <c r="AD28" t="n">
-        <v>-3818.3092</v>
+        <v>32.5742</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0388</v>
+        <v>39.8586</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0546</v>
+        <v>149.5455</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0834</v>
+        <v>329.0244</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>599.2032</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>12.9688</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>19.4757</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>25.5004</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-8316.8315</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>-5772.942</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-3793.6134</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.0809</v>
       </c>
     </row>
     <row r="29">
@@ -5161,91 +7597,121 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.882</v>
+        <v>0.997</v>
       </c>
       <c r="F29" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0294</v>
+        <v>0.0392</v>
       </c>
       <c r="H29" t="n">
-        <v>0.201</v>
+        <v>0.3943</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.3204</v>
       </c>
       <c r="J29" t="n">
-        <v>165.5331</v>
+        <v>0.016</v>
       </c>
       <c r="K29" t="n">
-        <v>309.8903</v>
+        <v>0.004</v>
       </c>
       <c r="L29" t="n">
-        <v>553.4417</v>
+        <v>0.024</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7808</v>
+        <v>0.0048</v>
       </c>
       <c r="N29" t="n">
-        <v>22.3856</v>
+        <v>0.405</v>
       </c>
       <c r="O29" t="n">
-        <v>28.4347</v>
+        <v>0.0155</v>
       </c>
       <c r="P29" t="n">
-        <v>152.6895</v>
+        <v>0.517</v>
       </c>
       <c r="Q29" t="n">
-        <v>362.7203</v>
+        <v>0.0158</v>
       </c>
       <c r="R29" t="n">
-        <v>610.8767</v>
+        <v>0.162</v>
       </c>
       <c r="S29" t="n">
-        <v>11.8858</v>
+        <v>0.0117</v>
       </c>
       <c r="T29" t="n">
-        <v>17.7414</v>
+        <v>159.8814</v>
       </c>
       <c r="U29" t="n">
-        <v>24.2747</v>
+        <v>332.3439</v>
       </c>
       <c r="V29" t="n">
-        <v>62.4963</v>
+        <v>605.4429</v>
       </c>
       <c r="W29" t="n">
-        <v>124.5074</v>
+        <v>15.0955</v>
       </c>
       <c r="X29" t="n">
-        <v>225.4416</v>
+        <v>21.5032</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.7529</v>
+        <v>28.3127</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.4729</v>
+        <v>108.897</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.4482</v>
+        <v>341.9332</v>
       </c>
       <c r="AB29" t="n">
-        <v>-788.283</v>
+        <v>611.9362</v>
       </c>
       <c r="AC29" t="n">
-        <v>-414.2717</v>
+        <v>10.4504</v>
       </c>
       <c r="AD29" t="n">
-        <v>-182.6777</v>
+        <v>16.9406</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.0487</v>
+        <v>23.898</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.06950000000000001</v>
+        <v>68.8327</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.1103</v>
+        <v>134.3386</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>237.405</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.8732</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>3.5791</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>7.8898</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-755.1923</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>-419.305</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-187.6002</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.1032</v>
       </c>
     </row>
     <row r="30">
@@ -5268,10 +7734,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.102</v>
+        <v>0.111</v>
       </c>
       <c r="F30" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="G30" t="n">
         <v>0.0196</v>
@@ -5280,79 +7746,109 @@
         <v>0.0392</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0019</v>
+        <v>0.0039</v>
       </c>
       <c r="J30" t="n">
-        <v>230.9169</v>
+        <v>0.032</v>
       </c>
       <c r="K30" t="n">
-        <v>433.6542</v>
+        <v>0.0056</v>
       </c>
       <c r="L30" t="n">
-        <v>702.5907999999999</v>
+        <v>0.032</v>
       </c>
       <c r="M30" t="n">
-        <v>18.3584</v>
+        <v>0.0056</v>
       </c>
       <c r="N30" t="n">
-        <v>35.1977</v>
+        <v>0.03</v>
       </c>
       <c r="O30" t="n">
-        <v>56.0068</v>
+        <v>0.0054</v>
       </c>
       <c r="P30" t="n">
-        <v>16.5411</v>
+        <v>0.012</v>
       </c>
       <c r="Q30" t="n">
-        <v>245.2495</v>
+        <v>0.0034</v>
       </c>
       <c r="R30" t="n">
-        <v>498.1551</v>
+        <v>0.002</v>
       </c>
       <c r="S30" t="n">
-        <v>13.6714</v>
+        <v>0.0014</v>
       </c>
       <c r="T30" t="n">
-        <v>30.3559</v>
+        <v>244.0612</v>
       </c>
       <c r="U30" t="n">
-        <v>51.6694</v>
+        <v>461.3528</v>
       </c>
       <c r="V30" t="n">
-        <v>4.4633</v>
+        <v>779.4043</v>
       </c>
       <c r="W30" t="n">
-        <v>11.6259</v>
+        <v>17.7829</v>
       </c>
       <c r="X30" t="n">
-        <v>22.9392</v>
+        <v>33.4442</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.851</v>
+        <v>53.6941</v>
       </c>
       <c r="Z30" t="n">
-        <v>16.6976</v>
+        <v>-42.7876</v>
       </c>
       <c r="AA30" t="n">
-        <v>36.1781</v>
+        <v>213.4914</v>
       </c>
       <c r="AB30" t="n">
-        <v>-654.1502</v>
+        <v>501.3288</v>
       </c>
       <c r="AC30" t="n">
-        <v>-383.8494</v>
+        <v>12.6791</v>
       </c>
       <c r="AD30" t="n">
-        <v>-179.9202</v>
+        <v>28.9971</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.0577</v>
+        <v>49.3828</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.082</v>
+        <v>3.9905</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.1311</v>
+        <v>10.8015</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>23.0477</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.1774</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>15.7906</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>34.5388</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-676.3836</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-351.3572</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-140.5143</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.1243</v>
       </c>
     </row>
     <row r="31">
@@ -5375,91 +7871,121 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="F31" t="n">
-        <v>0.538</v>
+        <v>0.357</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2794</v>
+        <v>0.1227</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8369</v>
+        <v>0.6019</v>
       </c>
       <c r="J31" t="n">
-        <v>-90.9383</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>13.9943</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>108.8316</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>22.8177</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>31.8926</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>41.5047</v>
+        <v>0.003</v>
       </c>
       <c r="P31" t="n">
-        <v>417.8372</v>
+        <v>0.285</v>
       </c>
       <c r="Q31" t="n">
-        <v>668.9257</v>
+        <v>0.0143</v>
       </c>
       <c r="R31" t="n">
-        <v>1008.1514</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>18.1968</v>
+        <v>0.0122</v>
       </c>
       <c r="T31" t="n">
-        <v>27.257</v>
+        <v>-88.15219999999999</v>
       </c>
       <c r="U31" t="n">
-        <v>37.0577</v>
+        <v>23.3637</v>
       </c>
       <c r="V31" t="n">
-        <v>234.9397</v>
+        <v>126.5827</v>
       </c>
       <c r="W31" t="n">
-        <v>436.5508</v>
+        <v>32.822</v>
       </c>
       <c r="X31" t="n">
-        <v>682.2999</v>
+        <v>40.7154</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.7991</v>
+        <v>49.351</v>
       </c>
       <c r="Z31" t="n">
-        <v>13.447</v>
+        <v>374.859</v>
       </c>
       <c r="AA31" t="n">
-        <v>22.9011</v>
+        <v>658.1061999999999</v>
       </c>
       <c r="AB31" t="n">
-        <v>-8630.2696</v>
+        <v>1024.3328</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6161.403</v>
+        <v>28.2479</v>
       </c>
       <c r="AD31" t="n">
-        <v>-4421.425</v>
+        <v>36.108</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0316</v>
+        <v>44.553</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0441</v>
+        <v>240.8812</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0648</v>
+        <v>455.927</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>755.5693</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>14.8639</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>23.1397</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>31.6318</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>-8743.251</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-6271.5145</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-4336.002</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.0619</v>
       </c>
     </row>
     <row r="32">
@@ -5482,91 +8008,121 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.989</v>
+        <v>0.992</v>
       </c>
       <c r="F32" t="n">
-        <v>0.466</v>
+        <v>0.498</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9639</v>
+        <v>0.988</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7456</v>
+        <v>0.7758</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1731</v>
+        <v>0.2077</v>
       </c>
       <c r="J32" t="n">
-        <v>324.7198</v>
+        <v>0.992</v>
       </c>
       <c r="K32" t="n">
-        <v>561.3892</v>
+        <v>0.0028</v>
       </c>
       <c r="L32" t="n">
-        <v>854.5234</v>
+        <v>0.991</v>
       </c>
       <c r="M32" t="n">
-        <v>28.4296</v>
+        <v>0.003</v>
       </c>
       <c r="N32" t="n">
-        <v>40.7046</v>
+        <v>0.847</v>
       </c>
       <c r="O32" t="n">
-        <v>56.3795</v>
+        <v>0.0114</v>
       </c>
       <c r="P32" t="n">
-        <v>-9.1525</v>
+        <v>0.478</v>
       </c>
       <c r="Q32" t="n">
-        <v>299.1998</v>
+        <v>0.0158</v>
       </c>
       <c r="R32" t="n">
-        <v>638.0936</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S32" t="n">
-        <v>23.5831</v>
+        <v>0.0081</v>
       </c>
       <c r="T32" t="n">
-        <v>36.1465</v>
+        <v>341.7722</v>
       </c>
       <c r="U32" t="n">
-        <v>51.8989</v>
+        <v>600.7388999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>963.6953999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>24.4032</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>38.899</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>55.664</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>-82.76739999999999</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>261.7674</v>
       </c>
       <c r="AB32" t="n">
-        <v>47.6288</v>
+        <v>623.1889</v>
       </c>
       <c r="AC32" t="n">
-        <v>86.0308</v>
+        <v>19.7361</v>
       </c>
       <c r="AD32" t="n">
-        <v>133.3441</v>
+        <v>34.284</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0567</v>
+        <v>51.1089</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1287</v>
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>47.8621</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>86.42789999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>133.2455</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="33">
@@ -5604,76 +8160,106 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>11.6214</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>163.8447</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>347.1019</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>87.6808</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>128.5711</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>182.2862</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>294.6986</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>671.7824000000001</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1204.8906</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>82.91249999999999</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>123.3485</v>
+        <v>2.6855</v>
       </c>
       <c r="U33" t="n">
-        <v>176.2527</v>
+        <v>156.5033</v>
       </c>
       <c r="V33" t="n">
-        <v>29.1705</v>
+        <v>338.9064</v>
       </c>
       <c r="W33" t="n">
-        <v>397.4199</v>
+        <v>87.7835</v>
       </c>
       <c r="X33" t="n">
-        <v>792.6673</v>
+        <v>127.3507</v>
       </c>
       <c r="Y33" t="n">
-        <v>45.8287</v>
+        <v>182.1587</v>
       </c>
       <c r="Z33" t="n">
-        <v>86.5689</v>
+        <v>296.6047</v>
       </c>
       <c r="AA33" t="n">
-        <v>142.6292</v>
+        <v>695.8787</v>
       </c>
       <c r="AB33" t="n">
-        <v>-6822.0958</v>
+        <v>1179.0994</v>
       </c>
       <c r="AC33" t="n">
-        <v>-4522.5369</v>
+        <v>82.9669</v>
       </c>
       <c r="AD33" t="n">
-        <v>-3074.0365</v>
+        <v>122.7105</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0134</v>
+        <v>177.4923</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0189</v>
+        <v>87.3582</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.0265</v>
+        <v>446.422</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>878.1552</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>46.7107</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>87.86750000000001</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>143.4038</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-6728.1585</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-4554.7262</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-2881.4567</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.027</v>
       </c>
     </row>
     <row r="34">
@@ -5696,91 +8282,121 @@
         <v>0.999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="F34" t="n">
-        <v>0.068</v>
+        <v>0.024</v>
       </c>
       <c r="G34" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0277</v>
+        <v>0.005</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1077</v>
+        <v>0.0423</v>
       </c>
       <c r="J34" t="n">
-        <v>98.423</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>244.2065</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>419.437</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>48.9076</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>61.8977</v>
+        <v>0.002</v>
       </c>
       <c r="O34" t="n">
-        <v>77.1735</v>
+        <v>0.0014</v>
       </c>
       <c r="P34" t="n">
-        <v>287.2874</v>
+        <v>0.026</v>
       </c>
       <c r="Q34" t="n">
-        <v>601.0382</v>
+        <v>0.005</v>
       </c>
       <c r="R34" t="n">
-        <v>1003.7764</v>
+        <v>0.056</v>
       </c>
       <c r="S34" t="n">
-        <v>43.6281</v>
+        <v>0.0073</v>
       </c>
       <c r="T34" t="n">
-        <v>56.9991</v>
+        <v>100.9145</v>
       </c>
       <c r="U34" t="n">
-        <v>72.3762</v>
+        <v>265.3826</v>
       </c>
       <c r="V34" t="n">
-        <v>143.3783</v>
+        <v>460.3501</v>
       </c>
       <c r="W34" t="n">
-        <v>315.0816</v>
+        <v>56.269</v>
       </c>
       <c r="X34" t="n">
-        <v>536.5626</v>
+        <v>69.34050000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.9239</v>
+        <v>84.6101</v>
       </c>
       <c r="Z34" t="n">
-        <v>20.9955</v>
+        <v>276.4458</v>
       </c>
       <c r="AA34" t="n">
-        <v>31.5004</v>
+        <v>580.8769</v>
       </c>
       <c r="AB34" t="n">
-        <v>-7021.2205</v>
+        <v>1014.1145</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4763.4307</v>
+        <v>50.8512</v>
       </c>
       <c r="AD34" t="n">
-        <v>-2886.8372</v>
+        <v>64.3416</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.0405</v>
+        <v>80.48520000000001</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0571</v>
+        <v>157.0369</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.0867</v>
+        <v>330.4875</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>576.3142</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>21.2154</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>30.1156</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>40.2426</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>-6973.2678</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-4653.7604</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-2920.872</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.0878</v>
       </c>
     </row>
     <row r="35">
@@ -5803,91 +8419,121 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.206</v>
+        <v>0.342</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0241</v>
+        <v>0.012</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1889</v>
+        <v>0.204</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2481</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>208.6346</v>
+        <v>0.008</v>
       </c>
       <c r="K35" t="n">
-        <v>411.155</v>
+        <v>0.0028</v>
       </c>
       <c r="L35" t="n">
-        <v>667.0032</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>36.7518</v>
+        <v>0.003</v>
       </c>
       <c r="N35" t="n">
-        <v>48.7663</v>
+        <v>0.151</v>
       </c>
       <c r="O35" t="n">
-        <v>64.5382</v>
+        <v>0.0113</v>
       </c>
       <c r="P35" t="n">
-        <v>150.5702</v>
+        <v>0.451</v>
       </c>
       <c r="Q35" t="n">
-        <v>440.7405</v>
+        <v>0.0157</v>
       </c>
       <c r="R35" t="n">
-        <v>787.0513</v>
+        <v>0.383</v>
       </c>
       <c r="S35" t="n">
-        <v>31.8892</v>
+        <v>0.0154</v>
       </c>
       <c r="T35" t="n">
-        <v>44.0853</v>
+        <v>221.0702</v>
       </c>
       <c r="U35" t="n">
-        <v>60.2165</v>
+        <v>440.6256</v>
       </c>
       <c r="V35" t="n">
-        <v>80.4615</v>
+        <v>746.2463</v>
       </c>
       <c r="W35" t="n">
-        <v>143.6298</v>
+        <v>33.5738</v>
       </c>
       <c r="X35" t="n">
-        <v>248.6587</v>
+        <v>47.2043</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.0118</v>
+        <v>63.8073</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.3314</v>
+        <v>95.1203</v>
       </c>
       <c r="AA35" t="n">
-        <v>15.6875</v>
+        <v>417.0778</v>
       </c>
       <c r="AB35" t="n">
-        <v>-856.4426</v>
+        <v>764.4097</v>
       </c>
       <c r="AC35" t="n">
-        <v>-474.6816</v>
+        <v>28.7035</v>
       </c>
       <c r="AD35" t="n">
-        <v>-237.427</v>
+        <v>42.6378</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.0469</v>
+        <v>59.4004</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.06850000000000001</v>
+        <v>84.443</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.1047</v>
+        <v>153.6668</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>273.0832</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.0976</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>7.6698</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>15.7501</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>-856.1008</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>-485.4833</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-234.1328</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.1035</v>
       </c>
     </row>
     <row r="36">
@@ -5925,76 +8571,106 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>305.8662</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>544.4965999999999</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>838.3368</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>52.2652</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>78.1871</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>115.1956</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.4308</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>314.1418</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>664.0700000000001</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>47.5699</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>73.1922</v>
+        <v>323.8761</v>
       </c>
       <c r="U36" t="n">
-        <v>109.61</v>
+        <v>587.6301</v>
       </c>
       <c r="V36" t="n">
-        <v>5.8679</v>
+        <v>948.1161</v>
       </c>
       <c r="W36" t="n">
-        <v>13.8895</v>
+        <v>47.0973</v>
       </c>
       <c r="X36" t="n">
-        <v>27.5116</v>
+        <v>74.081</v>
       </c>
       <c r="Y36" t="n">
-        <v>14.4307</v>
+        <v>111.4085</v>
       </c>
       <c r="Z36" t="n">
-        <v>36.5728</v>
+        <v>-70.09690000000001</v>
       </c>
       <c r="AA36" t="n">
-        <v>71.67359999999999</v>
+        <v>274.4564</v>
       </c>
       <c r="AB36" t="n">
-        <v>-895.6872</v>
+        <v>644.4358</v>
       </c>
       <c r="AC36" t="n">
-        <v>-493.9176</v>
+        <v>42.4146</v>
       </c>
       <c r="AD36" t="n">
-        <v>-233.488</v>
+        <v>69.46550000000001</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0567</v>
+        <v>107.035</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.082</v>
+        <v>5.1272</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.1287</v>
+        <v>13.1656</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>27.4983</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>13.2913</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>34.4248</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>70.0063</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-885.9485</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>-454.6549</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-189.0601</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="37">
@@ -6020,88 +8696,118 @@
         <v>0.998</v>
       </c>
       <c r="F37" t="n">
-        <v>0.26</v>
+        <v>0.136</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0378</v>
+        <v>0.0151</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4712</v>
+        <v>0.25</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.5763</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>112.0111</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>238.3842</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>55.3038</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>69.4335</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>86.6751</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>426.4121</v>
+        <v>0.045</v>
       </c>
       <c r="Q37" t="n">
-        <v>734.4619</v>
+        <v>0.0066</v>
       </c>
       <c r="R37" t="n">
-        <v>1146.3236</v>
+        <v>0.491</v>
       </c>
       <c r="S37" t="n">
-        <v>50.4451</v>
+        <v>0.0158</v>
       </c>
       <c r="T37" t="n">
-        <v>64.8188</v>
+        <v>-1.6025</v>
       </c>
       <c r="U37" t="n">
-        <v>82.02760000000001</v>
+        <v>121.0173</v>
       </c>
       <c r="V37" t="n">
-        <v>249.8288</v>
+        <v>266.8926</v>
       </c>
       <c r="W37" t="n">
-        <v>450.2174</v>
+        <v>63.2691</v>
       </c>
       <c r="X37" t="n">
-        <v>691.9383</v>
+        <v>77.29819999999999</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.1562</v>
+        <v>93.50409999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>28.1266</v>
+        <v>423.0694</v>
       </c>
       <c r="AA37" t="n">
-        <v>44.0765</v>
+        <v>723.0358</v>
       </c>
       <c r="AB37" t="n">
-        <v>-7548.8836</v>
+        <v>1152.4493</v>
       </c>
       <c r="AC37" t="n">
-        <v>-5275.5785</v>
+        <v>58.7772</v>
       </c>
       <c r="AD37" t="n">
-        <v>-3484.317</v>
+        <v>72.4538</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.0326</v>
+        <v>88.80710000000001</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.045</v>
+        <v>269.9933</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.06660000000000001</v>
+        <v>475.0305</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>767.9281999999999</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>24.9846</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>37.9506</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>52.3802</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-7507.6404</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-5247.9659</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-3537.6057</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -6124,91 +8830,121 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="F38" t="n">
-        <v>0.119</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6458</v>
+        <v>0.9062</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1414</v>
+        <v>0.4963</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.0259</v>
       </c>
       <c r="J38" t="n">
-        <v>376.2657</v>
+        <v>0.888</v>
       </c>
       <c r="K38" t="n">
-        <v>628.4983</v>
+        <v>0.01</v>
       </c>
       <c r="L38" t="n">
-        <v>931.7338</v>
+        <v>0.882</v>
       </c>
       <c r="M38" t="n">
-        <v>13.1844</v>
+        <v>0.0102</v>
       </c>
       <c r="N38" t="n">
-        <v>18.5342</v>
+        <v>0.601</v>
       </c>
       <c r="O38" t="n">
-        <v>24.0167</v>
+        <v>0.0155</v>
       </c>
       <c r="P38" t="n">
-        <v>11.5976</v>
+        <v>0.113</v>
       </c>
       <c r="Q38" t="n">
-        <v>331.3347</v>
+        <v>0.01</v>
       </c>
       <c r="R38" t="n">
-        <v>664.8013999999999</v>
+        <v>0.003</v>
       </c>
       <c r="S38" t="n">
-        <v>8.506600000000001</v>
+        <v>0.0017</v>
       </c>
       <c r="T38" t="n">
-        <v>14.0447</v>
+        <v>374.4495</v>
       </c>
       <c r="U38" t="n">
-        <v>19.4774</v>
+        <v>658.6025</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1032.2164</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>11.0104</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>17.8314</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>23.7686</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>-59.3806</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>288.2615</v>
       </c>
       <c r="AB38" t="n">
-        <v>49.0861</v>
+        <v>664.1527</v>
       </c>
       <c r="AC38" t="n">
-        <v>86.80800000000001</v>
+        <v>6.4758</v>
       </c>
       <c r="AD38" t="n">
-        <v>138.3115</v>
+        <v>13.3336</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.0574</v>
+        <v>19.1865</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0822</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.1314</v>
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>49.5109</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>87.3471</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>138.448</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.1261</v>
       </c>
     </row>
     <row r="39">
@@ -6231,91 +8967,121 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.162</v>
+        <v>0.431</v>
       </c>
       <c r="F39" t="n">
-        <v>0.041</v>
+        <v>0.171</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0312</v>
+        <v>0.0208</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0447</v>
+        <v>0.1811</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0399</v>
+        <v>0.1916</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.9843</v>
+        <v>0.059</v>
       </c>
       <c r="K39" t="n">
-        <v>205.011</v>
+        <v>0.0075</v>
       </c>
       <c r="L39" t="n">
-        <v>446.6961</v>
+        <v>0.064</v>
       </c>
       <c r="M39" t="n">
-        <v>19.0036</v>
+        <v>0.0077</v>
       </c>
       <c r="N39" t="n">
-        <v>42.0589</v>
+        <v>0.209</v>
       </c>
       <c r="O39" t="n">
-        <v>66.4816</v>
+        <v>0.0129</v>
       </c>
       <c r="P39" t="n">
-        <v>298.3419</v>
+        <v>0.231</v>
       </c>
       <c r="Q39" t="n">
-        <v>760.1337</v>
+        <v>0.0133</v>
       </c>
       <c r="R39" t="n">
-        <v>1254.1952</v>
+        <v>0.138</v>
       </c>
       <c r="S39" t="n">
-        <v>14.4893</v>
+        <v>0.0109</v>
       </c>
       <c r="T39" t="n">
-        <v>37.3877</v>
+        <v>-13.3399</v>
       </c>
       <c r="U39" t="n">
-        <v>61.84</v>
+        <v>201.5785</v>
       </c>
       <c r="V39" t="n">
-        <v>42.8043</v>
+        <v>461.5255</v>
       </c>
       <c r="W39" t="n">
-        <v>417.8233</v>
+        <v>16.8127</v>
       </c>
       <c r="X39" t="n">
-        <v>849.2727</v>
+        <v>41.5389</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.5023</v>
+        <v>65.95269999999999</v>
       </c>
       <c r="Z39" t="n">
-        <v>22.9415</v>
+        <v>274.1572</v>
       </c>
       <c r="AA39" t="n">
-        <v>47.4909</v>
+        <v>756.1171000000001</v>
       </c>
       <c r="AB39" t="n">
-        <v>-9791.030500000001</v>
+        <v>1278.0748</v>
       </c>
       <c r="AC39" t="n">
-        <v>-7166.4886</v>
+        <v>12.2829</v>
       </c>
       <c r="AD39" t="n">
-        <v>-4939.1436</v>
+        <v>36.6976</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.0134</v>
+        <v>61.6563</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.019</v>
+        <v>22.0057</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0269</v>
+        <v>453.6938</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>939.1396999999999</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-1.6469</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>23.8005</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>47.6582</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-9864.0965</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-7164.6163</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-5041.6066</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.0266</v>
       </c>
     </row>
     <row r="40">
@@ -6338,91 +9104,121 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.801</v>
+        <v>0.86</v>
       </c>
       <c r="F40" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0422</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="J40" t="n">
-        <v>-17.3473</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>161.2182</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>374.5232</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>15.9105</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>25.3182</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>34.4148</v>
+        <v>0.0081</v>
       </c>
       <c r="P40" t="n">
-        <v>426.7611</v>
+        <v>0.046</v>
       </c>
       <c r="Q40" t="n">
-        <v>795.4938</v>
+        <v>0.0066</v>
       </c>
       <c r="R40" t="n">
-        <v>1200.3278</v>
+        <v>0.003</v>
       </c>
       <c r="S40" t="n">
-        <v>10.789</v>
+        <v>0.0017</v>
       </c>
       <c r="T40" t="n">
-        <v>20.5152</v>
+        <v>-8.706799999999999</v>
       </c>
       <c r="U40" t="n">
-        <v>30.1408</v>
+        <v>180.104</v>
       </c>
       <c r="V40" t="n">
-        <v>248.1003</v>
+        <v>414.2421</v>
       </c>
       <c r="W40" t="n">
-        <v>461.7731</v>
+        <v>27.8627</v>
       </c>
       <c r="X40" t="n">
-        <v>714.3002</v>
+        <v>35.5271</v>
       </c>
       <c r="Y40" t="n">
-        <v>-2.7173</v>
+        <v>42.9234</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.6724</v>
+        <v>408.1785</v>
       </c>
       <c r="AA40" t="n">
-        <v>15.0717</v>
+        <v>766.2505</v>
       </c>
       <c r="AB40" t="n">
-        <v>-10445.3044</v>
+        <v>1205.3067</v>
       </c>
       <c r="AC40" t="n">
-        <v>-7750.6624</v>
+        <v>22.7764</v>
       </c>
       <c r="AD40" t="n">
-        <v>-5521.1063</v>
+        <v>30.73</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.0385</v>
+        <v>38.5425</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0545</v>
+        <v>248.9806</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.08450000000000001</v>
+        <v>477.1548</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>776.444</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>10.6887</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>17.5987</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>24.4874</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-10626.9127</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-7820.5567</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-5586.0046</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.0805</v>
       </c>
     </row>
     <row r="41">
@@ -6445,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.114</v>
+        <v>0.376</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -6460,76 +9256,106 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>241.4169</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>435.5598</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>705.9502</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>24.6207</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>31.1544</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>38.4312</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>213.8364</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>526.5104</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>846.3837</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>19.9423</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>26.3853</v>
+        <v>249.1205</v>
       </c>
       <c r="U41" t="n">
-        <v>33.8064</v>
+        <v>480.0783</v>
       </c>
       <c r="V41" t="n">
-        <v>92.9002</v>
+        <v>776.9606</v>
       </c>
       <c r="W41" t="n">
-        <v>179.1767</v>
+        <v>28.1244</v>
       </c>
       <c r="X41" t="n">
-        <v>326.5562</v>
+        <v>35.4405</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.7203</v>
+        <v>43.42</v>
       </c>
       <c r="Z41" t="n">
-        <v>12.278</v>
+        <v>149.1152</v>
       </c>
       <c r="AA41" t="n">
-        <v>18.286</v>
+        <v>469.0904</v>
       </c>
       <c r="AB41" t="n">
-        <v>-974.1597</v>
+        <v>822.2178</v>
       </c>
       <c r="AC41" t="n">
-        <v>-482.6239</v>
+        <v>23.1695</v>
       </c>
       <c r="AD41" t="n">
-        <v>-129.3609</v>
+        <v>30.5855</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.0523</v>
+        <v>39.2117</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0735</v>
+        <v>85.045</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.1151</v>
+        <v>174.9494</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>314.2369</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>12.3494</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>17.3655</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>24.0318</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-492.5315</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-145.2717</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>82.5314</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.1099</v>
       </c>
     </row>
     <row r="42">
@@ -6552,91 +9378,121 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.145</v>
+        <v>0.335</v>
       </c>
       <c r="F42" t="n">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0625</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0273</v>
+        <v>0.0471</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>358.8738</v>
+        <v>0.053</v>
       </c>
       <c r="K42" t="n">
-        <v>609.5016000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="L42" t="n">
-        <v>915.0922</v>
+        <v>0.054</v>
       </c>
       <c r="M42" t="n">
-        <v>17.3178</v>
+        <v>0.0071</v>
       </c>
       <c r="N42" t="n">
-        <v>39.243</v>
+        <v>0.046</v>
       </c>
       <c r="O42" t="n">
-        <v>65.5626</v>
+        <v>0.0066</v>
       </c>
       <c r="P42" t="n">
-        <v>22.1222</v>
+        <v>0.018</v>
       </c>
       <c r="Q42" t="n">
-        <v>346.8944</v>
+        <v>0.0042</v>
       </c>
       <c r="R42" t="n">
-        <v>692.0381</v>
+        <v>0.002</v>
       </c>
       <c r="S42" t="n">
-        <v>12.2324</v>
+        <v>0.0014</v>
       </c>
       <c r="T42" t="n">
-        <v>35.0778</v>
+        <v>353.6507</v>
       </c>
       <c r="U42" t="n">
-        <v>61.2914</v>
+        <v>640.5685</v>
       </c>
       <c r="V42" t="n">
-        <v>6.601</v>
+        <v>1021.5152</v>
       </c>
       <c r="W42" t="n">
-        <v>16.4037</v>
+        <v>16.2932</v>
       </c>
       <c r="X42" t="n">
-        <v>31.5611</v>
+        <v>37.4109</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.6891</v>
+        <v>64.02419999999999</v>
       </c>
       <c r="Z42" t="n">
-        <v>20.3002</v>
+        <v>-49.6764</v>
       </c>
       <c r="AA42" t="n">
-        <v>46.1001</v>
+        <v>304.8546</v>
       </c>
       <c r="AB42" t="n">
-        <v>-948.3561</v>
+        <v>692.3728</v>
       </c>
       <c r="AC42" t="n">
-        <v>-580.8629</v>
+        <v>11.6659</v>
       </c>
       <c r="AD42" t="n">
-        <v>-282.8031</v>
+        <v>32.8866</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.0574</v>
+        <v>59.8664</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0822</v>
+        <v>5.5379</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.1314</v>
+        <v>15.0666</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>31.2131</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-0.5335</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>19.5119</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>44.3633</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-942.2395</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>-522.3473</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-223.4105</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.1261</v>
       </c>
     </row>
     <row r="43">
@@ -6659,91 +9515,121 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.993</v>
+        <v>0.957</v>
       </c>
       <c r="F43" t="n">
-        <v>0.776</v>
+        <v>0.479</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07290000000000001</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7146</v>
+        <v>0.2333</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9601</v>
+        <v>0.7685</v>
       </c>
       <c r="J43" t="n">
-        <v>-141.9455</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-17.4198</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>124.1257</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>17.2269</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>26.9526</v>
+        <v>0.073</v>
       </c>
       <c r="O43" t="n">
-        <v>37.1804</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>624.0172</v>
+        <v>0.592</v>
       </c>
       <c r="Q43" t="n">
-        <v>978.4651</v>
+        <v>0.0155</v>
       </c>
       <c r="R43" t="n">
-        <v>1361.3294</v>
+        <v>0.854</v>
       </c>
       <c r="S43" t="n">
-        <v>12.3281</v>
+        <v>0.0112</v>
       </c>
       <c r="T43" t="n">
-        <v>22.1436</v>
+        <v>-130.1335</v>
       </c>
       <c r="U43" t="n">
-        <v>32.7989</v>
+        <v>11.3285</v>
       </c>
       <c r="V43" t="n">
-        <v>399.4111</v>
+        <v>150.071</v>
       </c>
       <c r="W43" t="n">
-        <v>644.4791</v>
+        <v>32.1829</v>
       </c>
       <c r="X43" t="n">
-        <v>923.898</v>
+        <v>40.3747</v>
       </c>
       <c r="Y43" t="n">
-        <v>-1.3535</v>
+        <v>49.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.324199999999999</v>
+        <v>601.8646</v>
       </c>
       <c r="AA43" t="n">
-        <v>18.0818</v>
+        <v>950.1418</v>
       </c>
       <c r="AB43" t="n">
-        <v>-11061.7113</v>
+        <v>1350.8178</v>
       </c>
       <c r="AC43" t="n">
-        <v>-8464.41</v>
+        <v>27.4511</v>
       </c>
       <c r="AD43" t="n">
-        <v>-6365.7162</v>
+        <v>35.7772</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.0316</v>
+        <v>44.595</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0437</v>
+        <v>385.0776</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.06419999999999999</v>
+        <v>656.4429</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>988.513</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>14.3526</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>22.4857</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>31.9331</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-10928.3113</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>-8214.989100000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>-6053.1627</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.0635</v>
       </c>
     </row>
     <row r="44">
@@ -6766,91 +9652,121 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.398</v>
+        <v>0.631</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9902</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6311</v>
+        <v>0.8956</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0761</v>
+        <v>0.3292</v>
       </c>
       <c r="J44" t="n">
-        <v>422.204</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>736.26</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1066.0612</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>28.4296</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>40.7046</v>
+        <v>0.989</v>
       </c>
       <c r="O44" t="n">
-        <v>56.3795</v>
+        <v>0.0033</v>
       </c>
       <c r="P44" t="n">
-        <v>-14.468</v>
+        <v>0.655</v>
       </c>
       <c r="Q44" t="n">
-        <v>387.184</v>
+        <v>0.015</v>
       </c>
       <c r="R44" t="n">
-        <v>772.9004</v>
+        <v>0.067</v>
       </c>
       <c r="S44" t="n">
-        <v>23.5831</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T44" t="n">
-        <v>36.1465</v>
+        <v>449.905</v>
       </c>
       <c r="U44" t="n">
-        <v>51.8989</v>
+        <v>765.4247</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1194.9173</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>24.4032</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>38.899</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>55.664</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>-102.1877</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>334.0843</v>
       </c>
       <c r="AB44" t="n">
-        <v>47.6473</v>
+        <v>757.8482</v>
       </c>
       <c r="AC44" t="n">
-        <v>86.22</v>
+        <v>19.7361</v>
       </c>
       <c r="AD44" t="n">
-        <v>132.6286</v>
+        <v>34.284</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.0566</v>
+        <v>51.1089</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0801</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1325</v>
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>47.971</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>86.39530000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>133.9737</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.1267</v>
       </c>
     </row>
     <row r="45">
@@ -6888,76 +9804,106 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>-25.759</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>151.5722</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>397.0414</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>76.3207</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>116.4913</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>173.864</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>433.5815</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>950.7023</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1456.0758</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>71.5925</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>111.9979</v>
+        <v>-30.6606</v>
       </c>
       <c r="U45" t="n">
-        <v>169.2435</v>
+        <v>156.4934</v>
       </c>
       <c r="V45" t="n">
-        <v>128.9007</v>
+        <v>398.8587</v>
       </c>
       <c r="W45" t="n">
-        <v>563.5567</v>
+        <v>76.5521</v>
       </c>
       <c r="X45" t="n">
-        <v>1015.305</v>
+        <v>116.3423</v>
       </c>
       <c r="Y45" t="n">
-        <v>35.7642</v>
+        <v>171.7664</v>
       </c>
       <c r="Z45" t="n">
-        <v>75.1437</v>
+        <v>432.0937</v>
       </c>
       <c r="AA45" t="n">
-        <v>133.581</v>
+        <v>950.1454</v>
       </c>
       <c r="AB45" t="n">
-        <v>-8695.659100000001</v>
+        <v>1426.9455</v>
       </c>
       <c r="AC45" t="n">
-        <v>-6151.9241</v>
+        <v>71.456</v>
       </c>
       <c r="AD45" t="n">
-        <v>-4330.2213</v>
+        <v>111.5869</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.0135</v>
+        <v>166.8705</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0191</v>
+        <v>161.8896</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.0276</v>
+        <v>602.4099</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1095.8958</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>37.0831</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>76.4298</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>133.2584</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>-8684.4689</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>-6226.8344</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>-4397.8095</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.0268</v>
       </c>
     </row>
     <row r="46">
@@ -6977,94 +9923,124 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="E46" t="n">
-        <v>0.908</v>
+        <v>0.96</v>
       </c>
       <c r="F46" t="n">
-        <v>0.049</v>
+        <v>0.038</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.068</v>
+        <v>0.0194</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0412</v>
+        <v>0.0617</v>
       </c>
       <c r="J46" t="n">
-        <v>90.0712</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>286.5306</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>519.2922</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>46.9509</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>60.2053</v>
+        <v>0.001</v>
       </c>
       <c r="O46" t="n">
-        <v>76.2033</v>
+        <v>0.001</v>
       </c>
       <c r="P46" t="n">
-        <v>413.4714</v>
+        <v>0.067</v>
       </c>
       <c r="Q46" t="n">
-        <v>818.7296</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="R46" t="n">
-        <v>1234.0876</v>
+        <v>0.032</v>
       </c>
       <c r="S46" t="n">
-        <v>41.951</v>
+        <v>0.0056</v>
       </c>
       <c r="T46" t="n">
-        <v>55.3235</v>
+        <v>93.1717</v>
       </c>
       <c r="U46" t="n">
-        <v>71.91289999999999</v>
+        <v>308.3357</v>
       </c>
       <c r="V46" t="n">
-        <v>232.93</v>
+        <v>551.6047</v>
       </c>
       <c r="W46" t="n">
-        <v>424.3754</v>
+        <v>55.3934</v>
       </c>
       <c r="X46" t="n">
-        <v>696.3638999999999</v>
+        <v>68.5994</v>
       </c>
       <c r="Y46" t="n">
-        <v>8.247400000000001</v>
+        <v>84.1511</v>
       </c>
       <c r="Z46" t="n">
-        <v>19.2868</v>
+        <v>368.8817</v>
       </c>
       <c r="AA46" t="n">
-        <v>30.5671</v>
+        <v>782.8038</v>
       </c>
       <c r="AB46" t="n">
-        <v>-9012.192800000001</v>
+        <v>1227.1831</v>
       </c>
       <c r="AC46" t="n">
-        <v>-6370.4017</v>
+        <v>50.0303</v>
       </c>
       <c r="AD46" t="n">
-        <v>-4133.3915</v>
+        <v>63.7456</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.0398</v>
+        <v>79.1876</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0567</v>
+        <v>237.7069</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.08649999999999999</v>
+        <v>449.659</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>734.1303</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>20.2511</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>29.8491</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>39.9563</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-8991.085999999999</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>-6420.7091</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>-4254.1523</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -7087,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.367</v>
+        <v>0.671</v>
       </c>
       <c r="F47" t="n">
         <v>0.001</v>
@@ -7096,82 +10072,112 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="J47" t="n">
-        <v>267.8324</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>507.9735</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>797.3016</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>48.9065</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>62.8755</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>79.4336</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>228.336</v>
+        <v>0.001</v>
       </c>
       <c r="Q47" t="n">
-        <v>607.4978</v>
+        <v>0.001</v>
       </c>
       <c r="R47" t="n">
-        <v>978.4773</v>
+        <v>0.004</v>
       </c>
       <c r="S47" t="n">
-        <v>44.0579</v>
+        <v>0.002</v>
       </c>
       <c r="T47" t="n">
-        <v>58.1115</v>
+        <v>301.3539</v>
       </c>
       <c r="U47" t="n">
-        <v>75.1721</v>
+        <v>553.5635</v>
       </c>
       <c r="V47" t="n">
-        <v>112.8472</v>
+        <v>902.3921</v>
       </c>
       <c r="W47" t="n">
-        <v>209.2217</v>
+        <v>51.0653</v>
       </c>
       <c r="X47" t="n">
-        <v>358.2001</v>
+        <v>66.5763</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.1363</v>
+        <v>83.8295</v>
       </c>
       <c r="Z47" t="n">
-        <v>21.3347</v>
+        <v>145.6915</v>
       </c>
       <c r="AA47" t="n">
-        <v>31.8266</v>
+        <v>542.1006</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1097.4174</v>
+        <v>945.5116</v>
       </c>
       <c r="AC47" t="n">
-        <v>-567.9248</v>
+        <v>46.0372</v>
       </c>
       <c r="AD47" t="n">
-        <v>-189.2476</v>
+        <v>61.7928</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.0509</v>
+        <v>79.1917</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0701</v>
+        <v>104.5919</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.1109</v>
+        <v>205.1684</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>357.649</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>18.4812</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>26.9465</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>37.3472</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-584.384</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>-199.7656</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>52.7408</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.1084</v>
       </c>
     </row>
     <row r="48">
@@ -7209,76 +10215,106 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>394.7266</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>717.3525</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1045.1119</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>56.0859</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>86.6083</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>129.0762</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4.5646</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>406.3339</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>804.5793</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>51.5054</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>81.8733</v>
+        <v>429.589</v>
       </c>
       <c r="U48" t="n">
-        <v>124.6692</v>
+        <v>747.6345</v>
       </c>
       <c r="V48" t="n">
-        <v>7.9108</v>
+        <v>1184.2085</v>
       </c>
       <c r="W48" t="n">
-        <v>18.1739</v>
+        <v>50.9539</v>
       </c>
       <c r="X48" t="n">
-        <v>35.2631</v>
+        <v>81.3291</v>
       </c>
       <c r="Y48" t="n">
-        <v>17.5883</v>
+        <v>123.4806</v>
       </c>
       <c r="Z48" t="n">
-        <v>45.2411</v>
+        <v>-87.26739999999999</v>
       </c>
       <c r="AA48" t="n">
-        <v>83.506</v>
+        <v>350.8414</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1129.4259</v>
+        <v>784.8058</v>
       </c>
       <c r="AC48" t="n">
-        <v>-656.9996</v>
+        <v>46.1191</v>
       </c>
       <c r="AD48" t="n">
-        <v>-354.363</v>
+        <v>76.7367</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.0566</v>
+        <v>118.3314</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.0801</v>
+        <v>6.6574</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1325</v>
+        <v>17.0245</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>34.4995</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>15.5507</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>42.0758</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>80.5568</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>-1105.6007</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-600.0823</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>-282.8706</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.1267</v>
       </c>
     </row>
     <row r="49">
@@ -7304,88 +10340,118 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.552</v>
+        <v>0.33</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2985</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8827</v>
+        <v>0.607</v>
       </c>
       <c r="J49" t="n">
-        <v>-55.2588</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>85.3433</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>243.7693</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>51.2933</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>65.572</v>
+        <v>0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>82.53440000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="P49" t="n">
-        <v>639.6885</v>
+        <v>0.277</v>
       </c>
       <c r="Q49" t="n">
-        <v>1026.517</v>
+        <v>0.0142</v>
       </c>
       <c r="R49" t="n">
-        <v>1438.0639</v>
+        <v>0.897</v>
       </c>
       <c r="S49" t="n">
-        <v>46.5175</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T49" t="n">
-        <v>61.0841</v>
+        <v>-38.3938</v>
       </c>
       <c r="U49" t="n">
-        <v>78.3578</v>
+        <v>113.3346</v>
       </c>
       <c r="V49" t="n">
-        <v>388.8818</v>
+        <v>277.1213</v>
       </c>
       <c r="W49" t="n">
-        <v>636.3796</v>
+        <v>63.6116</v>
       </c>
       <c r="X49" t="n">
-        <v>951.3113</v>
+        <v>77.9624</v>
       </c>
       <c r="Y49" t="n">
-        <v>10.1439</v>
+        <v>94.4081</v>
       </c>
       <c r="Z49" t="n">
-        <v>24.4041</v>
+        <v>600.5508</v>
       </c>
       <c r="AA49" t="n">
-        <v>40.3955</v>
+        <v>981.3228</v>
       </c>
       <c r="AB49" t="n">
-        <v>-9733.0677</v>
+        <v>1403.283</v>
       </c>
       <c r="AC49" t="n">
-        <v>-7180.7535</v>
+        <v>58.7043</v>
       </c>
       <c r="AD49" t="n">
-        <v>-5085.7276</v>
+        <v>73.2192</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.0323</v>
+        <v>89.2852</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0446</v>
+        <v>399.3361</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.0649</v>
+        <v>651.3816</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>985.5953</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>24.7887</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>38.5478</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>53.4596</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-9350.040499999999</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>-6870.4243</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>-4761.764</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.064</v>
       </c>
     </row>
   </sheetData>
